--- a/downloads/10.5281_zenodo.19682162/cb_hbm4eu_alignedstudies_adults.xlsx
+++ b/downloads/10.5281_zenodo.19682162/cb_hbm4eu_alignedstudies_adults.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="813">
   <si>
     <t xml:space="preserve">Varname</t>
   </si>
@@ -1454,15 +1454,6 @@
     <t xml:space="preserve">Calculated variable</t>
   </si>
   <si>
-    <t xml:space="preserve">MAKECOLUMN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constraints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VARNAME</t>
-  </si>
-  <si>
     <t xml:space="preserve">cd</t>
   </si>
   <si>
@@ -1483,18 +1474,12 @@
 -1 for X &lt; LOD</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;&lt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">cd_lod</t>
   </si>
   <si>
     <t xml:space="preserve">lod of cd associated with the measurement of the sample</t>
   </si>
   <si>
-    <t xml:space="preserve">Decimal data</t>
-  </si>
-  <si>
     <t xml:space="preserve">cd_loq</t>
   </si>
   <si>
@@ -1916,9 +1901,6 @@
   </si>
   <si>
     <t xml:space="preserve">N-Acetyl-S-(2-carbamoyl-2-hydroxyethyl)cysteine  (GAMA) level measured in the sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
   </si>
   <si>
     <t xml:space="preserve">gama_lod</t>
@@ -2187,9 +2169,6 @@
   </si>
   <si>
     <t xml:space="preserve">loq of ClF3CA associated with the measurement of the sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
   </si>
   <si>
     <t xml:space="preserve">Name of the data collection uploaded to the data platform with information regarding the age group, institution and name of the data collecion</t>
@@ -2723,25 +2702,23 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:P124" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:P124"/>
-  <tableColumns count="16">
-    <tableColumn id="1" name="MAKECOLUMN"/>
-    <tableColumn id="2" name="Constraints"/>
-    <tableColumn id="3" name="Varname"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Type"/>
-    <tableColumn id="6" name="Categories"/>
-    <tableColumn id="7" name="Unit"/>
-    <tableColumn id="8" name="AllowedValues"/>
-    <tableColumn id="9" name="MinValue"/>
-    <tableColumn id="10" name="MaxValue"/>
-    <tableColumn id="11" name="MissingsAllowed"/>
-    <tableColumn id="12" name="attention_providers"/>
-    <tableColumn id="13" name="Conditional"/>
-    <tableColumn id="14" name="Remarks"/>
-    <tableColumn id="15" name="DecimalsAfterComma"/>
-    <tableColumn id="16" name="Unique Identifier"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:N119" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:N119"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="Varname"/>
+    <tableColumn id="2" name="Description"/>
+    <tableColumn id="3" name="Type"/>
+    <tableColumn id="4" name="Categories"/>
+    <tableColumn id="5" name="Unit"/>
+    <tableColumn id="6" name="AllowedValues"/>
+    <tableColumn id="7" name="MinValue"/>
+    <tableColumn id="8" name="MaxValue"/>
+    <tableColumn id="9" name="MissingsAllowed"/>
+    <tableColumn id="10" name="attention_providers"/>
+    <tableColumn id="11" name="Conditional"/>
+    <tableColumn id="12" name="Remarks"/>
+    <tableColumn id="13" name="DecimalsAfterComma"/>
+    <tableColumn id="14" name="Unique Identifier"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8688,3997 +8665,3271 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="92.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="7.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="10.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="5.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="13.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="8.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="15.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="192.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="11.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="250.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="18.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="17.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="92.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="7.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="5.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="192.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="250.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>468</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2</v>
+      <c r="A2" t="s">
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>469</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
         <v>16</v>
       </c>
+      <c r="D2"/>
+      <c r="E2"/>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2"/>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2"/>
-      <c r="N2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2"/>
-      <c r="P2"/>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="s">
+        <v>467</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>468</v>
       </c>
       <c r="C3" t="s">
-        <v>470</v>
-      </c>
-      <c r="D3" t="s">
-        <v>471</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D3"/>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F3"/>
-      <c r="G3" t="s">
-        <v>62</v>
-      </c>
+      <c r="G3"/>
       <c r="H3"/>
       <c r="I3"/>
-      <c r="J3"/>
+      <c r="J3" t="s">
+        <v>469</v>
+      </c>
       <c r="K3"/>
       <c r="L3" t="s">
+        <v>470</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B4" t="s">
         <v>472</v>
       </c>
-      <c r="M3"/>
-      <c r="N3" t="s">
-        <v>473</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>474</v>
-      </c>
       <c r="C4" t="s">
-        <v>475</v>
-      </c>
-      <c r="D4" t="s">
-        <v>476</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D4"/>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F4"/>
-      <c r="G4" t="s">
-        <v>62</v>
-      </c>
+      <c r="G4"/>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
-      <c r="M4"/>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
       <c r="N4"/>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P4"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
+      <c r="A5" t="s">
+        <v>473</v>
       </c>
       <c r="B5" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C5" t="s">
-        <v>478</v>
-      </c>
-      <c r="D5" t="s">
-        <v>479</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D5"/>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F5"/>
-      <c r="G5" t="s">
-        <v>62</v>
-      </c>
+      <c r="G5"/>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5"/>
-      <c r="M5"/>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
       <c r="N5"/>
-      <c r="O5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P5"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
+      <c r="A6" t="s">
+        <v>475</v>
       </c>
       <c r="B6" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C6" t="s">
-        <v>480</v>
-      </c>
-      <c r="D6" t="s">
-        <v>481</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D6"/>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F6"/>
-      <c r="G6" t="s">
-        <v>62</v>
-      </c>
+      <c r="G6"/>
       <c r="H6"/>
       <c r="I6"/>
-      <c r="J6"/>
+      <c r="J6" t="s">
+        <v>469</v>
+      </c>
       <c r="K6"/>
       <c r="L6" t="s">
-        <v>472</v>
-      </c>
-      <c r="M6"/>
-      <c r="N6" t="s">
-        <v>473</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P6"/>
+        <v>470</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>1</v>
+      <c r="A7" t="s">
+        <v>477</v>
       </c>
       <c r="B7" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="C7" t="s">
-        <v>482</v>
-      </c>
-      <c r="D7" t="s">
-        <v>483</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D7"/>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F7"/>
-      <c r="G7" t="s">
-        <v>62</v>
-      </c>
+      <c r="G7"/>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7"/>
-      <c r="M7"/>
+      <c r="M7" t="n">
+        <v>4</v>
+      </c>
       <c r="N7"/>
-      <c r="O7" t="n">
-        <v>4</v>
-      </c>
-      <c r="P7"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>1</v>
+      <c r="A8" t="s">
+        <v>479</v>
       </c>
       <c r="B8" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>484</v>
-      </c>
-      <c r="D8" t="s">
-        <v>485</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D8"/>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F8"/>
-      <c r="G8" t="s">
-        <v>62</v>
-      </c>
+      <c r="G8"/>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8"/>
-      <c r="M8"/>
+      <c r="M8" t="n">
+        <v>4</v>
+      </c>
       <c r="N8"/>
-      <c r="O8" t="n">
-        <v>4</v>
-      </c>
-      <c r="P8"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>1</v>
+      <c r="A9" t="s">
+        <v>481</v>
       </c>
       <c r="B9" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C9" t="s">
-        <v>486</v>
-      </c>
-      <c r="D9" t="s">
-        <v>487</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D9"/>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F9"/>
-      <c r="G9" t="s">
-        <v>62</v>
-      </c>
+      <c r="G9"/>
       <c r="H9"/>
       <c r="I9"/>
-      <c r="J9"/>
+      <c r="J9" t="s">
+        <v>469</v>
+      </c>
       <c r="K9"/>
       <c r="L9" t="s">
-        <v>472</v>
-      </c>
-      <c r="M9"/>
-      <c r="N9" t="s">
-        <v>473</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9"/>
+        <v>470</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>1</v>
+      <c r="A10" t="s">
+        <v>483</v>
       </c>
       <c r="B10" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C10" t="s">
-        <v>488</v>
-      </c>
-      <c r="D10" t="s">
-        <v>489</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D10"/>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F10"/>
-      <c r="G10" t="s">
-        <v>62</v>
-      </c>
+      <c r="G10"/>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10"/>
-      <c r="M10"/>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
       <c r="N10"/>
-      <c r="O10" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
+      <c r="A11" t="s">
+        <v>485</v>
       </c>
       <c r="B11" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C11" t="s">
-        <v>490</v>
-      </c>
-      <c r="D11" t="s">
-        <v>491</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D11"/>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F11"/>
-      <c r="G11" t="s">
-        <v>62</v>
-      </c>
+      <c r="G11"/>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11"/>
-      <c r="M11"/>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
       <c r="N11"/>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
-      <c r="P11"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>1</v>
+      <c r="A12" t="s">
+        <v>487</v>
       </c>
       <c r="B12" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C12" t="s">
-        <v>492</v>
-      </c>
-      <c r="D12" t="s">
-        <v>493</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D12"/>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F12"/>
-      <c r="G12" t="s">
-        <v>62</v>
-      </c>
+      <c r="G12"/>
       <c r="H12"/>
       <c r="I12"/>
-      <c r="J12"/>
+      <c r="J12" t="s">
+        <v>469</v>
+      </c>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>472</v>
-      </c>
-      <c r="M12"/>
-      <c r="N12" t="s">
-        <v>473</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
-      <c r="P12"/>
+        <v>470</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>1</v>
+      <c r="A13" t="s">
+        <v>489</v>
       </c>
       <c r="B13" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C13" t="s">
-        <v>494</v>
-      </c>
-      <c r="D13" t="s">
-        <v>495</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D13"/>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F13"/>
-      <c r="G13" t="s">
-        <v>62</v>
-      </c>
+      <c r="G13"/>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13"/>
-      <c r="M13"/>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
       <c r="N13"/>
-      <c r="O13" t="n">
-        <v>4</v>
-      </c>
-      <c r="P13"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>1</v>
+      <c r="A14" t="s">
+        <v>491</v>
       </c>
       <c r="B14" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C14" t="s">
-        <v>496</v>
-      </c>
-      <c r="D14" t="s">
-        <v>497</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D14"/>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F14"/>
-      <c r="G14" t="s">
-        <v>62</v>
-      </c>
+      <c r="G14"/>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14"/>
-      <c r="M14"/>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
       <c r="N14"/>
-      <c r="O14" t="n">
-        <v>4</v>
-      </c>
-      <c r="P14"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>1</v>
+      <c r="A15" t="s">
+        <v>493</v>
       </c>
       <c r="B15" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C15" t="s">
-        <v>498</v>
-      </c>
-      <c r="D15" t="s">
-        <v>499</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D15"/>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F15"/>
-      <c r="G15" t="s">
-        <v>62</v>
-      </c>
+      <c r="G15"/>
       <c r="H15"/>
       <c r="I15"/>
-      <c r="J15"/>
+      <c r="J15" t="s">
+        <v>469</v>
+      </c>
       <c r="K15"/>
       <c r="L15" t="s">
-        <v>472</v>
-      </c>
-      <c r="M15"/>
-      <c r="N15" t="s">
-        <v>473</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15"/>
+        <v>470</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>1</v>
+      <c r="A16" t="s">
+        <v>495</v>
       </c>
       <c r="B16" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C16" t="s">
-        <v>500</v>
-      </c>
-      <c r="D16" t="s">
-        <v>501</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D16"/>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F16"/>
-      <c r="G16" t="s">
-        <v>62</v>
-      </c>
+      <c r="G16"/>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16"/>
-      <c r="M16"/>
+      <c r="M16" t="n">
+        <v>4</v>
+      </c>
       <c r="N16"/>
-      <c r="O16" t="n">
-        <v>4</v>
-      </c>
-      <c r="P16"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>1</v>
+      <c r="A17" t="s">
+        <v>497</v>
       </c>
       <c r="B17" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C17" t="s">
-        <v>502</v>
-      </c>
-      <c r="D17" t="s">
-        <v>503</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D17"/>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F17"/>
-      <c r="G17" t="s">
-        <v>62</v>
-      </c>
+      <c r="G17"/>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17"/>
-      <c r="M17"/>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
       <c r="N17"/>
-      <c r="O17" t="n">
-        <v>4</v>
-      </c>
-      <c r="P17"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>1</v>
+      <c r="A18" t="s">
+        <v>499</v>
       </c>
       <c r="B18" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C18" t="s">
-        <v>504</v>
-      </c>
-      <c r="D18" t="s">
-        <v>505</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D18"/>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F18"/>
-      <c r="G18" t="s">
-        <v>62</v>
-      </c>
+      <c r="G18"/>
       <c r="H18"/>
       <c r="I18"/>
-      <c r="J18"/>
+      <c r="J18" t="s">
+        <v>469</v>
+      </c>
       <c r="K18"/>
       <c r="L18" t="s">
-        <v>472</v>
-      </c>
-      <c r="M18"/>
-      <c r="N18" t="s">
-        <v>473</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18"/>
+        <v>470</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>1</v>
+      <c r="A19" t="s">
+        <v>501</v>
       </c>
       <c r="B19" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C19" t="s">
-        <v>506</v>
-      </c>
-      <c r="D19" t="s">
-        <v>507</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D19"/>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F19"/>
-      <c r="G19" t="s">
-        <v>62</v>
-      </c>
+      <c r="G19"/>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19"/>
-      <c r="M19"/>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
       <c r="N19"/>
-      <c r="O19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P19"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>1</v>
+      <c r="A20" t="s">
+        <v>503</v>
       </c>
       <c r="B20" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C20" t="s">
-        <v>508</v>
-      </c>
-      <c r="D20" t="s">
-        <v>509</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D20"/>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F20"/>
-      <c r="G20" t="s">
-        <v>62</v>
-      </c>
+      <c r="G20"/>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20"/>
-      <c r="M20"/>
+      <c r="M20" t="n">
+        <v>4</v>
+      </c>
       <c r="N20"/>
-      <c r="O20" t="n">
-        <v>4</v>
-      </c>
-      <c r="P20"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>1</v>
+      <c r="A21" t="s">
+        <v>505</v>
       </c>
       <c r="B21" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C21" t="s">
-        <v>510</v>
-      </c>
-      <c r="D21" t="s">
-        <v>511</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D21"/>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F21"/>
-      <c r="G21" t="s">
-        <v>62</v>
-      </c>
+      <c r="G21"/>
       <c r="H21"/>
       <c r="I21"/>
-      <c r="J21"/>
+      <c r="J21" t="s">
+        <v>469</v>
+      </c>
       <c r="K21"/>
       <c r="L21" t="s">
-        <v>472</v>
-      </c>
-      <c r="M21"/>
-      <c r="N21" t="s">
-        <v>473</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4</v>
-      </c>
-      <c r="P21"/>
+        <v>470</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21"/>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>1</v>
+      <c r="A22" t="s">
+        <v>507</v>
       </c>
       <c r="B22" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C22" t="s">
-        <v>512</v>
-      </c>
-      <c r="D22" t="s">
-        <v>513</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D22"/>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F22"/>
-      <c r="G22" t="s">
-        <v>62</v>
-      </c>
+      <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22"/>
-      <c r="M22"/>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
       <c r="N22"/>
-      <c r="O22" t="n">
-        <v>4</v>
-      </c>
-      <c r="P22"/>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>1</v>
+      <c r="A23" t="s">
+        <v>509</v>
       </c>
       <c r="B23" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C23" t="s">
-        <v>514</v>
-      </c>
-      <c r="D23" t="s">
-        <v>515</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D23"/>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F23"/>
-      <c r="G23" t="s">
-        <v>62</v>
-      </c>
+      <c r="G23"/>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23"/>
-      <c r="M23"/>
+      <c r="M23" t="n">
+        <v>4</v>
+      </c>
       <c r="N23"/>
-      <c r="O23" t="n">
-        <v>4</v>
-      </c>
-      <c r="P23"/>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>1</v>
+      <c r="A24" t="s">
+        <v>511</v>
       </c>
       <c r="B24" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C24" t="s">
-        <v>516</v>
-      </c>
-      <c r="D24" t="s">
-        <v>517</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D24"/>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F24"/>
-      <c r="G24" t="s">
-        <v>62</v>
-      </c>
+      <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
-      <c r="J24"/>
+      <c r="J24" t="s">
+        <v>469</v>
+      </c>
       <c r="K24"/>
       <c r="L24" t="s">
-        <v>472</v>
-      </c>
-      <c r="M24"/>
-      <c r="N24" t="s">
-        <v>473</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4</v>
-      </c>
-      <c r="P24"/>
+        <v>470</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24"/>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>1</v>
+      <c r="A25" t="s">
+        <v>513</v>
       </c>
       <c r="B25" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C25" t="s">
-        <v>518</v>
-      </c>
-      <c r="D25" t="s">
-        <v>519</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D25"/>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F25"/>
-      <c r="G25" t="s">
-        <v>62</v>
-      </c>
+      <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25"/>
-      <c r="M25"/>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
       <c r="N25"/>
-      <c r="O25" t="n">
-        <v>4</v>
-      </c>
-      <c r="P25"/>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>1</v>
+      <c r="A26" t="s">
+        <v>515</v>
       </c>
       <c r="B26" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C26" t="s">
-        <v>520</v>
-      </c>
-      <c r="D26" t="s">
-        <v>521</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D26"/>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F26"/>
-      <c r="G26" t="s">
-        <v>62</v>
-      </c>
+      <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26"/>
-      <c r="M26"/>
+      <c r="M26" t="n">
+        <v>4</v>
+      </c>
       <c r="N26"/>
-      <c r="O26" t="n">
-        <v>4</v>
-      </c>
-      <c r="P26"/>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>1</v>
+      <c r="A27" t="s">
+        <v>517</v>
       </c>
       <c r="B27" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C27" t="s">
-        <v>522</v>
-      </c>
-      <c r="D27" t="s">
-        <v>523</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D27"/>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F27"/>
-      <c r="G27" t="s">
-        <v>62</v>
-      </c>
+      <c r="G27"/>
       <c r="H27"/>
       <c r="I27"/>
-      <c r="J27"/>
+      <c r="J27" t="s">
+        <v>469</v>
+      </c>
       <c r="K27"/>
       <c r="L27" t="s">
-        <v>472</v>
-      </c>
-      <c r="M27"/>
-      <c r="N27" t="s">
-        <v>473</v>
-      </c>
-      <c r="O27" t="n">
-        <v>4</v>
-      </c>
-      <c r="P27"/>
+        <v>470</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N27"/>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>1</v>
+      <c r="A28" t="s">
+        <v>519</v>
       </c>
       <c r="B28" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C28" t="s">
-        <v>524</v>
-      </c>
-      <c r="D28" t="s">
-        <v>525</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D28"/>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F28"/>
-      <c r="G28" t="s">
-        <v>62</v>
-      </c>
+      <c r="G28"/>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28"/>
-      <c r="M28"/>
+      <c r="M28" t="n">
+        <v>4</v>
+      </c>
       <c r="N28"/>
-      <c r="O28" t="n">
-        <v>4</v>
-      </c>
-      <c r="P28"/>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>1</v>
+      <c r="A29" t="s">
+        <v>521</v>
       </c>
       <c r="B29" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C29" t="s">
-        <v>526</v>
-      </c>
-      <c r="D29" t="s">
-        <v>527</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D29"/>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F29"/>
-      <c r="G29" t="s">
-        <v>62</v>
-      </c>
+      <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
       <c r="L29"/>
-      <c r="M29"/>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
       <c r="N29"/>
-      <c r="O29" t="n">
-        <v>4</v>
-      </c>
-      <c r="P29"/>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>1</v>
+      <c r="A30" t="s">
+        <v>523</v>
       </c>
       <c r="B30" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C30" t="s">
-        <v>528</v>
-      </c>
-      <c r="D30" t="s">
-        <v>529</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D30"/>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F30"/>
-      <c r="G30" t="s">
-        <v>62</v>
-      </c>
+      <c r="G30"/>
       <c r="H30"/>
       <c r="I30"/>
-      <c r="J30"/>
+      <c r="J30" t="s">
+        <v>469</v>
+      </c>
       <c r="K30"/>
       <c r="L30" t="s">
-        <v>472</v>
-      </c>
-      <c r="M30"/>
-      <c r="N30" t="s">
-        <v>473</v>
-      </c>
-      <c r="O30" t="n">
-        <v>4</v>
-      </c>
-      <c r="P30"/>
+        <v>470</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>1</v>
+      <c r="A31" t="s">
+        <v>525</v>
       </c>
       <c r="B31" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="C31" t="s">
-        <v>530</v>
-      </c>
-      <c r="D31" t="s">
-        <v>513</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D31"/>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F31"/>
-      <c r="G31" t="s">
-        <v>62</v>
-      </c>
+      <c r="G31"/>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31"/>
-      <c r="M31"/>
+      <c r="M31" t="n">
+        <v>4</v>
+      </c>
       <c r="N31"/>
-      <c r="O31" t="n">
-        <v>4</v>
-      </c>
-      <c r="P31"/>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>1</v>
+      <c r="A32" t="s">
+        <v>526</v>
       </c>
       <c r="B32" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="C32" t="s">
-        <v>531</v>
-      </c>
-      <c r="D32" t="s">
-        <v>515</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D32"/>
       <c r="E32" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F32"/>
-      <c r="G32" t="s">
-        <v>62</v>
-      </c>
+      <c r="G32"/>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32"/>
-      <c r="M32"/>
+      <c r="M32" t="n">
+        <v>4</v>
+      </c>
       <c r="N32"/>
-      <c r="O32" t="n">
-        <v>4</v>
-      </c>
-      <c r="P32"/>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>1</v>
+      <c r="A33" t="s">
+        <v>527</v>
       </c>
       <c r="B33" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C33" t="s">
-        <v>532</v>
-      </c>
-      <c r="D33" t="s">
-        <v>533</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D33"/>
       <c r="E33" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F33"/>
-      <c r="G33" t="s">
-        <v>62</v>
-      </c>
+      <c r="G33"/>
       <c r="H33"/>
       <c r="I33"/>
-      <c r="J33"/>
+      <c r="J33" t="s">
+        <v>469</v>
+      </c>
       <c r="K33"/>
       <c r="L33" t="s">
-        <v>472</v>
-      </c>
-      <c r="M33"/>
-      <c r="N33" t="s">
-        <v>473</v>
-      </c>
-      <c r="O33" t="n">
-        <v>4</v>
-      </c>
-      <c r="P33"/>
+        <v>470</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4</v>
+      </c>
+      <c r="N33"/>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>1</v>
+      <c r="A34" t="s">
+        <v>529</v>
       </c>
       <c r="B34" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C34" t="s">
-        <v>534</v>
-      </c>
-      <c r="D34" t="s">
-        <v>535</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D34"/>
       <c r="E34" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F34"/>
-      <c r="G34" t="s">
-        <v>62</v>
-      </c>
+      <c r="G34"/>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34"/>
-      <c r="M34"/>
+      <c r="M34" t="n">
+        <v>4</v>
+      </c>
       <c r="N34"/>
-      <c r="O34" t="n">
-        <v>4</v>
-      </c>
-      <c r="P34"/>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>1</v>
+      <c r="A35" t="s">
+        <v>531</v>
       </c>
       <c r="B35" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C35" t="s">
-        <v>536</v>
-      </c>
-      <c r="D35" t="s">
-        <v>537</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D35"/>
       <c r="E35" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F35"/>
-      <c r="G35" t="s">
-        <v>62</v>
-      </c>
+      <c r="G35"/>
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35"/>
-      <c r="M35"/>
+      <c r="M35" t="n">
+        <v>4</v>
+      </c>
       <c r="N35"/>
-      <c r="O35" t="n">
-        <v>4</v>
-      </c>
-      <c r="P35"/>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>1</v>
+      <c r="A36" t="s">
+        <v>533</v>
       </c>
       <c r="B36" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C36" t="s">
-        <v>538</v>
-      </c>
-      <c r="D36" t="s">
-        <v>539</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D36"/>
       <c r="E36" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F36"/>
-      <c r="G36" t="s">
-        <v>62</v>
-      </c>
+      <c r="G36"/>
       <c r="H36"/>
       <c r="I36"/>
-      <c r="J36"/>
+      <c r="J36" t="s">
+        <v>469</v>
+      </c>
       <c r="K36"/>
       <c r="L36" t="s">
-        <v>472</v>
-      </c>
-      <c r="M36"/>
-      <c r="N36" t="s">
-        <v>473</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4</v>
-      </c>
-      <c r="P36"/>
+        <v>470</v>
+      </c>
+      <c r="M36" t="n">
+        <v>4</v>
+      </c>
+      <c r="N36"/>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>1</v>
+      <c r="A37" t="s">
+        <v>535</v>
       </c>
       <c r="B37" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C37" t="s">
-        <v>540</v>
-      </c>
-      <c r="D37" t="s">
-        <v>541</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D37"/>
       <c r="E37" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F37"/>
-      <c r="G37" t="s">
-        <v>62</v>
-      </c>
+      <c r="G37"/>
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37"/>
       <c r="K37"/>
       <c r="L37"/>
-      <c r="M37"/>
+      <c r="M37" t="n">
+        <v>4</v>
+      </c>
       <c r="N37"/>
-      <c r="O37" t="n">
-        <v>4</v>
-      </c>
-      <c r="P37"/>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>1</v>
+      <c r="A38" t="s">
+        <v>537</v>
       </c>
       <c r="B38" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C38" t="s">
-        <v>542</v>
-      </c>
-      <c r="D38" t="s">
-        <v>543</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D38"/>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F38"/>
-      <c r="G38" t="s">
-        <v>62</v>
-      </c>
+      <c r="G38"/>
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38"/>
-      <c r="M38"/>
+      <c r="M38" t="n">
+        <v>4</v>
+      </c>
       <c r="N38"/>
-      <c r="O38" t="n">
-        <v>4</v>
-      </c>
-      <c r="P38"/>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>1</v>
+      <c r="A39" t="s">
+        <v>539</v>
       </c>
       <c r="B39" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C39" t="s">
-        <v>544</v>
-      </c>
-      <c r="D39" t="s">
-        <v>545</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D39"/>
       <c r="E39" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F39"/>
-      <c r="G39" t="s">
-        <v>62</v>
-      </c>
+      <c r="G39"/>
       <c r="H39"/>
       <c r="I39"/>
-      <c r="J39"/>
+      <c r="J39" t="s">
+        <v>469</v>
+      </c>
       <c r="K39"/>
       <c r="L39" t="s">
-        <v>472</v>
-      </c>
-      <c r="M39"/>
-      <c r="N39" t="s">
-        <v>473</v>
-      </c>
-      <c r="O39" t="n">
-        <v>4</v>
-      </c>
-      <c r="P39"/>
+        <v>470</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4</v>
+      </c>
+      <c r="N39"/>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>1</v>
+      <c r="A40" t="s">
+        <v>541</v>
       </c>
       <c r="B40" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C40" t="s">
-        <v>546</v>
-      </c>
-      <c r="D40" t="s">
-        <v>547</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D40"/>
       <c r="E40" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F40"/>
-      <c r="G40" t="s">
-        <v>62</v>
-      </c>
+      <c r="G40"/>
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40"/>
-      <c r="M40"/>
+      <c r="M40" t="n">
+        <v>4</v>
+      </c>
       <c r="N40"/>
-      <c r="O40" t="n">
-        <v>4</v>
-      </c>
-      <c r="P40"/>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>1</v>
+      <c r="A41" t="s">
+        <v>543</v>
       </c>
       <c r="B41" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C41" t="s">
-        <v>548</v>
-      </c>
-      <c r="D41" t="s">
-        <v>549</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D41"/>
       <c r="E41" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F41"/>
-      <c r="G41" t="s">
-        <v>62</v>
-      </c>
+      <c r="G41"/>
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41"/>
-      <c r="M41"/>
+      <c r="M41" t="n">
+        <v>4</v>
+      </c>
       <c r="N41"/>
-      <c r="O41" t="n">
-        <v>4</v>
-      </c>
-      <c r="P41"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>1</v>
+      <c r="A42" t="s">
+        <v>545</v>
       </c>
       <c r="B42" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C42" t="s">
-        <v>550</v>
-      </c>
-      <c r="D42" t="s">
-        <v>551</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D42"/>
       <c r="E42" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F42"/>
-      <c r="G42" t="s">
-        <v>62</v>
-      </c>
+      <c r="G42"/>
       <c r="H42"/>
       <c r="I42"/>
-      <c r="J42"/>
+      <c r="J42" t="s">
+        <v>469</v>
+      </c>
       <c r="K42"/>
       <c r="L42" t="s">
-        <v>472</v>
-      </c>
-      <c r="M42"/>
-      <c r="N42" t="s">
-        <v>473</v>
-      </c>
-      <c r="O42" t="n">
-        <v>4</v>
-      </c>
-      <c r="P42"/>
+        <v>470</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4</v>
+      </c>
+      <c r="N42"/>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>1</v>
+      <c r="A43" t="s">
+        <v>547</v>
       </c>
       <c r="B43" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C43" t="s">
-        <v>552</v>
-      </c>
-      <c r="D43" t="s">
-        <v>553</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D43"/>
       <c r="E43" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F43"/>
-      <c r="G43" t="s">
-        <v>62</v>
-      </c>
+      <c r="G43"/>
       <c r="H43"/>
       <c r="I43"/>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43"/>
-      <c r="M43"/>
+      <c r="M43" t="n">
+        <v>4</v>
+      </c>
       <c r="N43"/>
-      <c r="O43" t="n">
-        <v>4</v>
-      </c>
-      <c r="P43"/>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>1</v>
+      <c r="A44" t="s">
+        <v>549</v>
       </c>
       <c r="B44" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C44" t="s">
-        <v>554</v>
-      </c>
-      <c r="D44" t="s">
-        <v>555</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D44"/>
       <c r="E44" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F44"/>
-      <c r="G44" t="s">
-        <v>62</v>
-      </c>
+      <c r="G44"/>
       <c r="H44"/>
       <c r="I44"/>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44"/>
-      <c r="M44"/>
+      <c r="M44" t="n">
+        <v>4</v>
+      </c>
       <c r="N44"/>
-      <c r="O44" t="n">
-        <v>4</v>
-      </c>
-      <c r="P44"/>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>1</v>
+      <c r="A45" t="s">
+        <v>551</v>
       </c>
       <c r="B45" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C45" t="s">
-        <v>556</v>
-      </c>
-      <c r="D45" t="s">
-        <v>557</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D45"/>
       <c r="E45" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F45"/>
-      <c r="G45" t="s">
-        <v>62</v>
-      </c>
+      <c r="G45"/>
       <c r="H45"/>
       <c r="I45"/>
-      <c r="J45"/>
+      <c r="J45" t="s">
+        <v>469</v>
+      </c>
       <c r="K45"/>
       <c r="L45" t="s">
-        <v>472</v>
-      </c>
-      <c r="M45"/>
-      <c r="N45" t="s">
-        <v>473</v>
-      </c>
-      <c r="O45" t="n">
-        <v>4</v>
-      </c>
-      <c r="P45"/>
+        <v>470</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4</v>
+      </c>
+      <c r="N45"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>1</v>
+      <c r="A46" t="s">
+        <v>553</v>
       </c>
       <c r="B46" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C46" t="s">
-        <v>558</v>
-      </c>
-      <c r="D46" t="s">
-        <v>559</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D46"/>
       <c r="E46" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F46"/>
-      <c r="G46" t="s">
-        <v>62</v>
-      </c>
+      <c r="G46"/>
       <c r="H46"/>
       <c r="I46"/>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46"/>
-      <c r="M46"/>
+      <c r="M46" t="n">
+        <v>4</v>
+      </c>
       <c r="N46"/>
-      <c r="O46" t="n">
-        <v>4</v>
-      </c>
-      <c r="P46"/>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>1</v>
+      <c r="A47" t="s">
+        <v>555</v>
       </c>
       <c r="B47" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C47" t="s">
-        <v>560</v>
-      </c>
-      <c r="D47" t="s">
-        <v>561</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D47"/>
       <c r="E47" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F47"/>
-      <c r="G47" t="s">
-        <v>62</v>
-      </c>
+      <c r="G47"/>
       <c r="H47"/>
       <c r="I47"/>
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47"/>
-      <c r="M47"/>
+      <c r="M47" t="n">
+        <v>4</v>
+      </c>
       <c r="N47"/>
-      <c r="O47" t="n">
-        <v>4</v>
-      </c>
-      <c r="P47"/>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>1</v>
+      <c r="A48" t="s">
+        <v>557</v>
       </c>
       <c r="B48" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C48" t="s">
-        <v>562</v>
-      </c>
-      <c r="D48" t="s">
-        <v>563</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D48"/>
       <c r="E48" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F48"/>
-      <c r="G48" t="s">
-        <v>62</v>
-      </c>
+      <c r="G48"/>
       <c r="H48"/>
       <c r="I48"/>
-      <c r="J48"/>
+      <c r="J48" t="s">
+        <v>469</v>
+      </c>
       <c r="K48"/>
       <c r="L48" t="s">
-        <v>472</v>
-      </c>
-      <c r="M48"/>
-      <c r="N48" t="s">
-        <v>473</v>
-      </c>
-      <c r="O48" t="n">
-        <v>4</v>
-      </c>
-      <c r="P48"/>
+        <v>470</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4</v>
+      </c>
+      <c r="N48"/>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>1</v>
+      <c r="A49" t="s">
+        <v>559</v>
       </c>
       <c r="B49" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C49" t="s">
-        <v>564</v>
-      </c>
-      <c r="D49" t="s">
-        <v>565</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D49"/>
       <c r="E49" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F49"/>
-      <c r="G49" t="s">
-        <v>62</v>
-      </c>
+      <c r="G49"/>
       <c r="H49"/>
       <c r="I49"/>
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49"/>
-      <c r="M49"/>
+      <c r="M49" t="n">
+        <v>4</v>
+      </c>
       <c r="N49"/>
-      <c r="O49" t="n">
-        <v>4</v>
-      </c>
-      <c r="P49"/>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>1</v>
+      <c r="A50" t="s">
+        <v>561</v>
       </c>
       <c r="B50" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C50" t="s">
-        <v>566</v>
-      </c>
-      <c r="D50" t="s">
-        <v>567</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D50"/>
       <c r="E50" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F50"/>
-      <c r="G50" t="s">
-        <v>62</v>
-      </c>
+      <c r="G50"/>
       <c r="H50"/>
       <c r="I50"/>
       <c r="J50"/>
       <c r="K50"/>
       <c r="L50"/>
-      <c r="M50"/>
+      <c r="M50" t="n">
+        <v>4</v>
+      </c>
       <c r="N50"/>
-      <c r="O50" t="n">
-        <v>4</v>
-      </c>
-      <c r="P50"/>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>1</v>
+      <c r="A51" t="s">
+        <v>563</v>
       </c>
       <c r="B51" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C51" t="s">
-        <v>568</v>
-      </c>
-      <c r="D51" t="s">
-        <v>569</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D51"/>
       <c r="E51" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F51"/>
-      <c r="G51" t="s">
-        <v>62</v>
-      </c>
+      <c r="G51"/>
       <c r="H51"/>
       <c r="I51"/>
-      <c r="J51"/>
+      <c r="J51" t="s">
+        <v>469</v>
+      </c>
       <c r="K51"/>
       <c r="L51" t="s">
-        <v>472</v>
-      </c>
-      <c r="M51"/>
-      <c r="N51" t="s">
-        <v>473</v>
-      </c>
-      <c r="O51" t="n">
-        <v>4</v>
-      </c>
-      <c r="P51"/>
+        <v>470</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4</v>
+      </c>
+      <c r="N51"/>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>1</v>
+      <c r="A52" t="s">
+        <v>565</v>
       </c>
       <c r="B52" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C52" t="s">
-        <v>570</v>
-      </c>
-      <c r="D52" t="s">
-        <v>571</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D52"/>
       <c r="E52" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F52"/>
-      <c r="G52" t="s">
-        <v>62</v>
-      </c>
+      <c r="G52"/>
       <c r="H52"/>
       <c r="I52"/>
       <c r="J52"/>
       <c r="K52"/>
       <c r="L52"/>
-      <c r="M52"/>
+      <c r="M52" t="n">
+        <v>4</v>
+      </c>
       <c r="N52"/>
-      <c r="O52" t="n">
-        <v>4</v>
-      </c>
-      <c r="P52"/>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>1</v>
+      <c r="A53" t="s">
+        <v>567</v>
       </c>
       <c r="B53" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C53" t="s">
-        <v>572</v>
-      </c>
-      <c r="D53" t="s">
-        <v>573</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D53"/>
       <c r="E53" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F53"/>
-      <c r="G53" t="s">
-        <v>62</v>
-      </c>
+      <c r="G53"/>
       <c r="H53"/>
       <c r="I53"/>
       <c r="J53"/>
       <c r="K53"/>
       <c r="L53"/>
-      <c r="M53"/>
+      <c r="M53" t="n">
+        <v>4</v>
+      </c>
       <c r="N53"/>
-      <c r="O53" t="n">
-        <v>4</v>
-      </c>
-      <c r="P53"/>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>1</v>
+      <c r="A54" t="s">
+        <v>569</v>
       </c>
       <c r="B54" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C54" t="s">
-        <v>574</v>
-      </c>
-      <c r="D54" t="s">
-        <v>575</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D54"/>
       <c r="E54" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F54"/>
-      <c r="G54" t="s">
-        <v>62</v>
-      </c>
+      <c r="G54"/>
       <c r="H54"/>
       <c r="I54"/>
-      <c r="J54"/>
+      <c r="J54" t="s">
+        <v>469</v>
+      </c>
       <c r="K54"/>
       <c r="L54" t="s">
-        <v>472</v>
-      </c>
-      <c r="M54"/>
-      <c r="N54" t="s">
-        <v>473</v>
-      </c>
-      <c r="O54" t="n">
-        <v>4</v>
-      </c>
-      <c r="P54"/>
+        <v>470</v>
+      </c>
+      <c r="M54" t="n">
+        <v>4</v>
+      </c>
+      <c r="N54"/>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>1</v>
+      <c r="A55" t="s">
+        <v>571</v>
       </c>
       <c r="B55" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C55" t="s">
-        <v>576</v>
-      </c>
-      <c r="D55" t="s">
-        <v>577</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D55"/>
       <c r="E55" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F55"/>
-      <c r="G55" t="s">
-        <v>62</v>
-      </c>
+      <c r="G55"/>
       <c r="H55"/>
       <c r="I55"/>
       <c r="J55"/>
       <c r="K55"/>
       <c r="L55"/>
-      <c r="M55"/>
+      <c r="M55" t="n">
+        <v>4</v>
+      </c>
       <c r="N55"/>
-      <c r="O55" t="n">
-        <v>4</v>
-      </c>
-      <c r="P55"/>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>1</v>
+      <c r="A56" t="s">
+        <v>573</v>
       </c>
       <c r="B56" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C56" t="s">
-        <v>578</v>
-      </c>
-      <c r="D56" t="s">
-        <v>579</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D56"/>
       <c r="E56" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F56"/>
-      <c r="G56" t="s">
-        <v>62</v>
-      </c>
+      <c r="G56"/>
       <c r="H56"/>
       <c r="I56"/>
       <c r="J56"/>
       <c r="K56"/>
       <c r="L56"/>
-      <c r="M56"/>
+      <c r="M56" t="n">
+        <v>4</v>
+      </c>
       <c r="N56"/>
-      <c r="O56" t="n">
-        <v>4</v>
-      </c>
-      <c r="P56"/>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>1</v>
+      <c r="A57" t="s">
+        <v>575</v>
       </c>
       <c r="B57" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C57" t="s">
-        <v>580</v>
-      </c>
-      <c r="D57" t="s">
-        <v>581</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D57"/>
       <c r="E57" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F57"/>
-      <c r="G57" t="s">
-        <v>62</v>
-      </c>
+      <c r="G57"/>
       <c r="H57"/>
       <c r="I57"/>
-      <c r="J57"/>
+      <c r="J57" t="s">
+        <v>469</v>
+      </c>
       <c r="K57"/>
       <c r="L57" t="s">
-        <v>472</v>
-      </c>
-      <c r="M57"/>
-      <c r="N57" t="s">
-        <v>473</v>
-      </c>
-      <c r="O57" t="n">
-        <v>4</v>
-      </c>
-      <c r="P57"/>
+        <v>470</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4</v>
+      </c>
+      <c r="N57"/>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>1</v>
+      <c r="A58" t="s">
+        <v>577</v>
       </c>
       <c r="B58" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C58" t="s">
-        <v>582</v>
-      </c>
-      <c r="D58" t="s">
-        <v>583</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D58"/>
       <c r="E58" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F58"/>
-      <c r="G58" t="s">
-        <v>62</v>
-      </c>
+      <c r="G58"/>
       <c r="H58"/>
       <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
       <c r="L58"/>
-      <c r="M58"/>
+      <c r="M58" t="n">
+        <v>4</v>
+      </c>
       <c r="N58"/>
-      <c r="O58" t="n">
-        <v>4</v>
-      </c>
-      <c r="P58"/>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>1</v>
+      <c r="A59" t="s">
+        <v>579</v>
       </c>
       <c r="B59" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C59" t="s">
-        <v>584</v>
-      </c>
-      <c r="D59" t="s">
-        <v>585</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D59"/>
       <c r="E59" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F59"/>
-      <c r="G59" t="s">
-        <v>62</v>
-      </c>
+      <c r="G59"/>
       <c r="H59"/>
       <c r="I59"/>
       <c r="J59"/>
       <c r="K59"/>
       <c r="L59"/>
-      <c r="M59"/>
+      <c r="M59" t="n">
+        <v>4</v>
+      </c>
       <c r="N59"/>
-      <c r="O59" t="n">
-        <v>4</v>
-      </c>
-      <c r="P59"/>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>1</v>
+      <c r="A60" t="s">
+        <v>581</v>
       </c>
       <c r="B60" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C60" t="s">
-        <v>586</v>
-      </c>
-      <c r="D60" t="s">
-        <v>587</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D60"/>
       <c r="E60" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F60"/>
-      <c r="G60" t="s">
-        <v>62</v>
-      </c>
+      <c r="G60"/>
       <c r="H60"/>
       <c r="I60"/>
-      <c r="J60"/>
+      <c r="J60" t="s">
+        <v>469</v>
+      </c>
       <c r="K60"/>
       <c r="L60" t="s">
-        <v>472</v>
-      </c>
-      <c r="M60"/>
-      <c r="N60" t="s">
-        <v>473</v>
-      </c>
-      <c r="O60" t="n">
-        <v>4</v>
-      </c>
-      <c r="P60"/>
+        <v>470</v>
+      </c>
+      <c r="M60" t="n">
+        <v>4</v>
+      </c>
+      <c r="N60"/>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>1</v>
+      <c r="A61" t="s">
+        <v>583</v>
       </c>
       <c r="B61" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C61" t="s">
-        <v>588</v>
-      </c>
-      <c r="D61" t="s">
-        <v>589</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D61"/>
       <c r="E61" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F61"/>
-      <c r="G61" t="s">
-        <v>62</v>
-      </c>
+      <c r="G61"/>
       <c r="H61"/>
       <c r="I61"/>
       <c r="J61"/>
       <c r="K61"/>
       <c r="L61"/>
-      <c r="M61"/>
+      <c r="M61" t="n">
+        <v>4</v>
+      </c>
       <c r="N61"/>
-      <c r="O61" t="n">
-        <v>4</v>
-      </c>
-      <c r="P61"/>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>1</v>
+      <c r="A62" t="s">
+        <v>585</v>
       </c>
       <c r="B62" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C62" t="s">
-        <v>590</v>
-      </c>
-      <c r="D62" t="s">
-        <v>591</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D62"/>
       <c r="E62" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F62"/>
-      <c r="G62" t="s">
-        <v>62</v>
-      </c>
+      <c r="G62"/>
       <c r="H62"/>
       <c r="I62"/>
       <c r="J62"/>
       <c r="K62"/>
       <c r="L62"/>
-      <c r="M62"/>
+      <c r="M62" t="n">
+        <v>4</v>
+      </c>
       <c r="N62"/>
-      <c r="O62" t="n">
-        <v>4</v>
-      </c>
-      <c r="P62"/>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>1</v>
+      <c r="A63" t="s">
+        <v>587</v>
       </c>
       <c r="B63" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C63" t="s">
-        <v>592</v>
-      </c>
-      <c r="D63" t="s">
-        <v>593</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D63"/>
       <c r="E63" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F63"/>
-      <c r="G63" t="s">
-        <v>62</v>
-      </c>
+      <c r="G63"/>
       <c r="H63"/>
       <c r="I63"/>
-      <c r="J63"/>
+      <c r="J63" t="s">
+        <v>469</v>
+      </c>
       <c r="K63"/>
       <c r="L63" t="s">
-        <v>472</v>
-      </c>
-      <c r="M63"/>
-      <c r="N63" t="s">
-        <v>473</v>
-      </c>
-      <c r="O63" t="n">
-        <v>4</v>
-      </c>
-      <c r="P63"/>
+        <v>470</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4</v>
+      </c>
+      <c r="N63"/>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>1</v>
+      <c r="A64" t="s">
+        <v>589</v>
       </c>
       <c r="B64" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C64" t="s">
-        <v>594</v>
-      </c>
-      <c r="D64" t="s">
-        <v>595</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D64"/>
       <c r="E64" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F64"/>
-      <c r="G64" t="s">
-        <v>62</v>
-      </c>
+      <c r="G64"/>
       <c r="H64"/>
       <c r="I64"/>
       <c r="J64"/>
       <c r="K64"/>
       <c r="L64"/>
-      <c r="M64"/>
+      <c r="M64" t="n">
+        <v>4</v>
+      </c>
       <c r="N64"/>
-      <c r="O64" t="n">
-        <v>4</v>
-      </c>
-      <c r="P64"/>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>1</v>
+      <c r="A65" t="s">
+        <v>591</v>
       </c>
       <c r="B65" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C65" t="s">
-        <v>596</v>
-      </c>
-      <c r="D65" t="s">
-        <v>597</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D65"/>
       <c r="E65" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F65"/>
-      <c r="G65" t="s">
-        <v>62</v>
-      </c>
+      <c r="G65"/>
       <c r="H65"/>
       <c r="I65"/>
       <c r="J65"/>
       <c r="K65"/>
       <c r="L65"/>
-      <c r="M65"/>
+      <c r="M65" t="n">
+        <v>4</v>
+      </c>
       <c r="N65"/>
-      <c r="O65" t="n">
-        <v>4</v>
-      </c>
-      <c r="P65"/>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>1</v>
+      <c r="A66" t="s">
+        <v>593</v>
       </c>
       <c r="B66" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C66" t="s">
-        <v>598</v>
-      </c>
-      <c r="D66" t="s">
-        <v>599</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D66"/>
       <c r="E66" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F66"/>
-      <c r="G66" t="s">
-        <v>62</v>
-      </c>
+      <c r="G66"/>
       <c r="H66"/>
       <c r="I66"/>
-      <c r="J66"/>
+      <c r="J66" t="s">
+        <v>469</v>
+      </c>
       <c r="K66"/>
       <c r="L66" t="s">
-        <v>472</v>
-      </c>
-      <c r="M66"/>
-      <c r="N66" t="s">
-        <v>473</v>
-      </c>
-      <c r="O66" t="n">
-        <v>4</v>
-      </c>
-      <c r="P66"/>
+        <v>470</v>
+      </c>
+      <c r="M66" t="n">
+        <v>4</v>
+      </c>
+      <c r="N66"/>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>1</v>
+      <c r="A67" t="s">
+        <v>595</v>
       </c>
       <c r="B67" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C67" t="s">
-        <v>600</v>
-      </c>
-      <c r="D67" t="s">
-        <v>601</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D67"/>
       <c r="E67" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F67"/>
-      <c r="G67" t="s">
-        <v>62</v>
-      </c>
+      <c r="G67"/>
       <c r="H67"/>
       <c r="I67"/>
       <c r="J67"/>
       <c r="K67"/>
       <c r="L67"/>
-      <c r="M67"/>
+      <c r="M67" t="n">
+        <v>4</v>
+      </c>
       <c r="N67"/>
-      <c r="O67" t="n">
-        <v>4</v>
-      </c>
-      <c r="P67"/>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>1</v>
+      <c r="A68" t="s">
+        <v>597</v>
       </c>
       <c r="B68" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C68" t="s">
-        <v>602</v>
-      </c>
-      <c r="D68" t="s">
-        <v>603</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D68"/>
       <c r="E68" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F68"/>
-      <c r="G68" t="s">
-        <v>62</v>
-      </c>
+      <c r="G68"/>
       <c r="H68"/>
       <c r="I68"/>
       <c r="J68"/>
       <c r="K68"/>
       <c r="L68"/>
-      <c r="M68"/>
+      <c r="M68" t="n">
+        <v>4</v>
+      </c>
       <c r="N68"/>
-      <c r="O68" t="n">
-        <v>4</v>
-      </c>
-      <c r="P68"/>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>1</v>
+      <c r="A69" t="s">
+        <v>599</v>
       </c>
       <c r="B69" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C69" t="s">
-        <v>604</v>
-      </c>
-      <c r="D69" t="s">
-        <v>605</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D69"/>
       <c r="E69" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F69"/>
-      <c r="G69" t="s">
-        <v>62</v>
-      </c>
+      <c r="G69"/>
       <c r="H69"/>
       <c r="I69"/>
-      <c r="J69"/>
+      <c r="J69" t="s">
+        <v>469</v>
+      </c>
       <c r="K69"/>
       <c r="L69" t="s">
-        <v>472</v>
-      </c>
-      <c r="M69"/>
-      <c r="N69" t="s">
-        <v>473</v>
-      </c>
-      <c r="O69" t="n">
-        <v>4</v>
-      </c>
-      <c r="P69"/>
+        <v>470</v>
+      </c>
+      <c r="M69" t="n">
+        <v>4</v>
+      </c>
+      <c r="N69"/>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>1</v>
+      <c r="A70" t="s">
+        <v>601</v>
       </c>
       <c r="B70" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C70" t="s">
-        <v>606</v>
-      </c>
-      <c r="D70" t="s">
-        <v>607</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D70"/>
       <c r="E70" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F70"/>
-      <c r="G70" t="s">
-        <v>62</v>
-      </c>
+      <c r="G70"/>
       <c r="H70"/>
       <c r="I70"/>
       <c r="J70"/>
       <c r="K70"/>
-      <c r="L70"/>
-      <c r="M70"/>
-      <c r="N70" t="s">
-        <v>473</v>
-      </c>
-      <c r="O70" t="n">
-        <v>4</v>
-      </c>
-      <c r="P70"/>
+      <c r="L70" t="s">
+        <v>470</v>
+      </c>
+      <c r="M70" t="n">
+        <v>4</v>
+      </c>
+      <c r="N70"/>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>1</v>
+      <c r="A71" t="s">
+        <v>603</v>
       </c>
       <c r="B71" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C71" t="s">
-        <v>608</v>
-      </c>
-      <c r="D71" t="s">
-        <v>609</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D71"/>
       <c r="E71" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F71"/>
-      <c r="G71" t="s">
-        <v>62</v>
-      </c>
+      <c r="G71"/>
       <c r="H71"/>
       <c r="I71"/>
       <c r="J71"/>
       <c r="K71"/>
       <c r="L71"/>
-      <c r="M71"/>
+      <c r="M71" t="n">
+        <v>4</v>
+      </c>
       <c r="N71"/>
-      <c r="O71" t="n">
-        <v>4</v>
-      </c>
-      <c r="P71"/>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>1</v>
+      <c r="A72" t="s">
+        <v>605</v>
       </c>
       <c r="B72" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C72" t="s">
-        <v>610</v>
-      </c>
-      <c r="D72" t="s">
-        <v>611</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D72"/>
       <c r="E72" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F72"/>
-      <c r="G72" t="s">
-        <v>62</v>
-      </c>
+      <c r="G72"/>
       <c r="H72"/>
       <c r="I72"/>
-      <c r="J72"/>
+      <c r="J72" t="s">
+        <v>607</v>
+      </c>
       <c r="K72"/>
       <c r="L72" t="s">
-        <v>612</v>
-      </c>
-      <c r="M72"/>
-      <c r="N72" t="s">
-        <v>473</v>
-      </c>
-      <c r="O72" t="n">
-        <v>4</v>
-      </c>
-      <c r="P72"/>
+        <v>470</v>
+      </c>
+      <c r="M72" t="n">
+        <v>4</v>
+      </c>
+      <c r="N72"/>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>1</v>
+      <c r="A73" t="s">
+        <v>608</v>
       </c>
       <c r="B73" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="C73" t="s">
-        <v>613</v>
-      </c>
-      <c r="D73" t="s">
-        <v>614</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D73"/>
       <c r="E73" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F73"/>
-      <c r="G73" t="s">
-        <v>62</v>
-      </c>
+      <c r="G73"/>
       <c r="H73"/>
       <c r="I73"/>
       <c r="J73"/>
       <c r="K73"/>
       <c r="L73"/>
-      <c r="M73"/>
+      <c r="M73" t="n">
+        <v>4</v>
+      </c>
       <c r="N73"/>
-      <c r="O73" t="n">
-        <v>4</v>
-      </c>
-      <c r="P73"/>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>1</v>
+      <c r="A74" t="s">
+        <v>610</v>
       </c>
       <c r="B74" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="C74" t="s">
-        <v>615</v>
-      </c>
-      <c r="D74" t="s">
-        <v>616</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D74"/>
       <c r="E74" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F74"/>
-      <c r="G74" t="s">
-        <v>62</v>
-      </c>
+      <c r="G74"/>
       <c r="H74"/>
       <c r="I74"/>
       <c r="J74"/>
       <c r="K74"/>
       <c r="L74"/>
-      <c r="M74"/>
+      <c r="M74" t="n">
+        <v>4</v>
+      </c>
       <c r="N74"/>
-      <c r="O74" t="n">
-        <v>4</v>
-      </c>
-      <c r="P74"/>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>1</v>
+      <c r="A75" t="s">
+        <v>612</v>
       </c>
       <c r="B75" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C75" t="s">
-        <v>617</v>
-      </c>
-      <c r="D75" t="s">
-        <v>618</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D75"/>
       <c r="E75" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F75"/>
-      <c r="G75" t="s">
-        <v>62</v>
-      </c>
+      <c r="G75"/>
       <c r="H75"/>
       <c r="I75"/>
-      <c r="J75"/>
+      <c r="J75" t="s">
+        <v>469</v>
+      </c>
       <c r="K75"/>
       <c r="L75" t="s">
-        <v>472</v>
-      </c>
-      <c r="M75"/>
-      <c r="N75" t="s">
-        <v>473</v>
-      </c>
-      <c r="O75" t="n">
-        <v>4</v>
-      </c>
-      <c r="P75"/>
+        <v>470</v>
+      </c>
+      <c r="M75" t="n">
+        <v>4</v>
+      </c>
+      <c r="N75"/>
     </row>
     <row r="76">
-      <c r="A76"/>
+      <c r="A76" t="s">
+        <v>614</v>
+      </c>
       <c r="B76" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C76" t="s">
-        <v>620</v>
-      </c>
-      <c r="D76" t="s">
-        <v>621</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D76"/>
       <c r="E76" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F76"/>
-      <c r="G76" t="s">
-        <v>62</v>
-      </c>
+      <c r="G76"/>
       <c r="H76"/>
       <c r="I76"/>
       <c r="J76"/>
       <c r="K76"/>
       <c r="L76"/>
-      <c r="M76"/>
+      <c r="M76" t="n">
+        <v>4</v>
+      </c>
       <c r="N76"/>
-      <c r="O76" t="n">
-        <v>4</v>
-      </c>
-      <c r="P76"/>
     </row>
     <row r="77">
-      <c r="A77"/>
+      <c r="A77" t="s">
+        <v>616</v>
+      </c>
       <c r="B77" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C77" t="s">
-        <v>622</v>
-      </c>
-      <c r="D77" t="s">
-        <v>623</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D77"/>
       <c r="E77" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F77"/>
-      <c r="G77" t="s">
-        <v>62</v>
-      </c>
+      <c r="G77"/>
       <c r="H77"/>
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77"/>
       <c r="L77"/>
-      <c r="M77"/>
+      <c r="M77" t="n">
+        <v>4</v>
+      </c>
       <c r="N77"/>
-      <c r="O77" t="n">
-        <v>4</v>
-      </c>
-      <c r="P77"/>
     </row>
     <row r="78">
-      <c r="A78"/>
+      <c r="A78" t="s">
+        <v>618</v>
+      </c>
       <c r="B78" t="s">
         <v>619</v>
       </c>
       <c r="C78" t="s">
-        <v>624</v>
-      </c>
-      <c r="D78" t="s">
-        <v>625</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D78"/>
       <c r="E78" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F78"/>
-      <c r="G78" t="s">
-        <v>62</v>
-      </c>
+      <c r="G78"/>
       <c r="H78"/>
       <c r="I78"/>
-      <c r="J78"/>
+      <c r="J78" t="s">
+        <v>469</v>
+      </c>
       <c r="K78"/>
       <c r="L78" t="s">
-        <v>472</v>
-      </c>
-      <c r="M78"/>
-      <c r="N78" t="s">
-        <v>473</v>
-      </c>
-      <c r="O78" t="n">
-        <v>4</v>
-      </c>
-      <c r="P78"/>
+        <v>470</v>
+      </c>
+      <c r="M78" t="n">
+        <v>4</v>
+      </c>
+      <c r="N78"/>
     </row>
     <row r="79">
-      <c r="A79"/>
+      <c r="A79" t="s">
+        <v>620</v>
+      </c>
       <c r="B79" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C79" t="s">
-        <v>626</v>
-      </c>
-      <c r="D79" t="s">
-        <v>627</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D79"/>
       <c r="E79" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F79"/>
-      <c r="G79" t="s">
-        <v>62</v>
-      </c>
+      <c r="G79"/>
       <c r="H79"/>
       <c r="I79"/>
       <c r="J79"/>
       <c r="K79"/>
       <c r="L79"/>
-      <c r="M79"/>
+      <c r="M79" t="n">
+        <v>4</v>
+      </c>
       <c r="N79"/>
-      <c r="O79" t="n">
-        <v>4</v>
-      </c>
-      <c r="P79"/>
     </row>
     <row r="80">
-      <c r="A80"/>
+      <c r="A80" t="s">
+        <v>622</v>
+      </c>
       <c r="B80" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C80" t="s">
-        <v>628</v>
-      </c>
-      <c r="D80" t="s">
-        <v>629</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D80"/>
       <c r="E80" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F80"/>
-      <c r="G80" t="s">
-        <v>62</v>
-      </c>
+      <c r="G80"/>
       <c r="H80"/>
       <c r="I80"/>
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80"/>
-      <c r="M80"/>
+      <c r="M80" t="n">
+        <v>4</v>
+      </c>
       <c r="N80"/>
-      <c r="O80" t="n">
-        <v>4</v>
-      </c>
-      <c r="P80"/>
     </row>
     <row r="81">
-      <c r="A81"/>
+      <c r="A81" t="s">
+        <v>624</v>
+      </c>
       <c r="B81" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="C81" t="s">
-        <v>630</v>
-      </c>
-      <c r="D81" t="s">
-        <v>631</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D81"/>
       <c r="E81" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F81"/>
-      <c r="G81" t="s">
-        <v>62</v>
-      </c>
+      <c r="G81"/>
       <c r="H81"/>
       <c r="I81"/>
-      <c r="J81"/>
+      <c r="J81" t="s">
+        <v>626</v>
+      </c>
       <c r="K81"/>
       <c r="L81" t="s">
-        <v>632</v>
-      </c>
-      <c r="M81"/>
-      <c r="N81" t="s">
-        <v>473</v>
-      </c>
-      <c r="O81" t="n">
-        <v>4</v>
-      </c>
-      <c r="P81"/>
+        <v>470</v>
+      </c>
+      <c r="M81" t="n">
+        <v>4</v>
+      </c>
+      <c r="N81"/>
     </row>
     <row r="82">
-      <c r="A82"/>
+      <c r="A82" t="s">
+        <v>627</v>
+      </c>
       <c r="B82" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="C82" t="s">
-        <v>633</v>
-      </c>
-      <c r="D82" t="s">
-        <v>634</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D82"/>
       <c r="E82" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F82"/>
-      <c r="G82" t="s">
-        <v>62</v>
-      </c>
+      <c r="G82"/>
       <c r="H82"/>
       <c r="I82"/>
       <c r="J82"/>
       <c r="K82"/>
       <c r="L82"/>
-      <c r="M82"/>
+      <c r="M82" t="n">
+        <v>4</v>
+      </c>
       <c r="N82"/>
-      <c r="O82" t="n">
-        <v>4</v>
-      </c>
-      <c r="P82"/>
     </row>
     <row r="83">
-      <c r="A83"/>
+      <c r="A83" t="s">
+        <v>629</v>
+      </c>
       <c r="B83" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="C83" t="s">
-        <v>635</v>
-      </c>
-      <c r="D83" t="s">
-        <v>636</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D83"/>
       <c r="E83" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F83"/>
-      <c r="G83" t="s">
-        <v>62</v>
-      </c>
+      <c r="G83"/>
       <c r="H83"/>
       <c r="I83"/>
       <c r="J83"/>
       <c r="K83"/>
       <c r="L83"/>
-      <c r="M83"/>
+      <c r="M83" t="n">
+        <v>4</v>
+      </c>
       <c r="N83"/>
-      <c r="O83" t="n">
-        <v>4</v>
-      </c>
-      <c r="P83"/>
     </row>
     <row r="84">
-      <c r="A84"/>
+      <c r="A84" t="s">
+        <v>631</v>
+      </c>
       <c r="B84" t="s">
-        <v>619</v>
+        <v>632</v>
       </c>
       <c r="C84" t="s">
-        <v>637</v>
-      </c>
-      <c r="D84" t="s">
-        <v>638</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D84"/>
       <c r="E84" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F84"/>
-      <c r="G84" t="s">
-        <v>62</v>
-      </c>
+      <c r="G84"/>
       <c r="H84"/>
       <c r="I84"/>
-      <c r="J84"/>
+      <c r="J84" t="s">
+        <v>469</v>
+      </c>
       <c r="K84"/>
       <c r="L84" t="s">
-        <v>472</v>
-      </c>
-      <c r="M84"/>
-      <c r="N84" t="s">
-        <v>473</v>
-      </c>
-      <c r="O84" t="n">
-        <v>4</v>
-      </c>
-      <c r="P84"/>
+        <v>470</v>
+      </c>
+      <c r="M84" t="n">
+        <v>4</v>
+      </c>
+      <c r="N84"/>
     </row>
     <row r="85">
-      <c r="A85"/>
+      <c r="A85" t="s">
+        <v>633</v>
+      </c>
       <c r="B85" t="s">
-        <v>619</v>
+        <v>634</v>
       </c>
       <c r="C85" t="s">
-        <v>639</v>
-      </c>
-      <c r="D85" t="s">
-        <v>640</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D85"/>
       <c r="E85" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F85"/>
-      <c r="G85" t="s">
-        <v>62</v>
-      </c>
+      <c r="G85"/>
       <c r="H85"/>
       <c r="I85"/>
       <c r="J85"/>
       <c r="K85"/>
       <c r="L85"/>
-      <c r="M85"/>
+      <c r="M85" t="n">
+        <v>4</v>
+      </c>
       <c r="N85"/>
-      <c r="O85" t="n">
-        <v>4</v>
-      </c>
-      <c r="P85"/>
     </row>
     <row r="86">
-      <c r="A86"/>
+      <c r="A86" t="s">
+        <v>635</v>
+      </c>
       <c r="B86" t="s">
-        <v>619</v>
+        <v>636</v>
       </c>
       <c r="C86" t="s">
-        <v>641</v>
-      </c>
-      <c r="D86" t="s">
-        <v>642</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D86"/>
       <c r="E86" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F86"/>
-      <c r="G86" t="s">
-        <v>62</v>
-      </c>
+      <c r="G86"/>
       <c r="H86"/>
       <c r="I86"/>
       <c r="J86"/>
       <c r="K86"/>
       <c r="L86"/>
-      <c r="M86"/>
+      <c r="M86" t="n">
+        <v>4</v>
+      </c>
       <c r="N86"/>
-      <c r="O86" t="n">
-        <v>4</v>
-      </c>
-      <c r="P86"/>
     </row>
     <row r="87">
-      <c r="A87"/>
+      <c r="A87" t="s">
+        <v>637</v>
+      </c>
       <c r="B87" t="s">
-        <v>619</v>
+        <v>638</v>
       </c>
       <c r="C87" t="s">
-        <v>643</v>
-      </c>
-      <c r="D87" t="s">
-        <v>644</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D87"/>
       <c r="E87" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F87"/>
-      <c r="G87" t="s">
-        <v>62</v>
-      </c>
+      <c r="G87"/>
       <c r="H87"/>
       <c r="I87"/>
-      <c r="J87"/>
+      <c r="J87" t="s">
+        <v>626</v>
+      </c>
       <c r="K87"/>
       <c r="L87" t="s">
-        <v>632</v>
-      </c>
-      <c r="M87"/>
-      <c r="N87" t="s">
-        <v>473</v>
-      </c>
-      <c r="O87" t="n">
-        <v>4</v>
-      </c>
-      <c r="P87"/>
+        <v>470</v>
+      </c>
+      <c r="M87" t="n">
+        <v>4</v>
+      </c>
+      <c r="N87"/>
     </row>
     <row r="88">
-      <c r="A88"/>
+      <c r="A88" t="s">
+        <v>639</v>
+      </c>
       <c r="B88" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="C88" t="s">
-        <v>645</v>
-      </c>
-      <c r="D88" t="s">
-        <v>646</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D88"/>
       <c r="E88" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F88"/>
-      <c r="G88" t="s">
-        <v>62</v>
-      </c>
+      <c r="G88"/>
       <c r="H88"/>
       <c r="I88"/>
       <c r="J88"/>
       <c r="K88"/>
       <c r="L88"/>
-      <c r="M88"/>
+      <c r="M88" t="n">
+        <v>4</v>
+      </c>
       <c r="N88"/>
-      <c r="O88" t="n">
-        <v>4</v>
-      </c>
-      <c r="P88"/>
     </row>
     <row r="89">
-      <c r="A89"/>
+      <c r="A89" t="s">
+        <v>641</v>
+      </c>
       <c r="B89" t="s">
-        <v>619</v>
+        <v>642</v>
       </c>
       <c r="C89" t="s">
-        <v>647</v>
-      </c>
-      <c r="D89" t="s">
-        <v>648</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D89"/>
       <c r="E89" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F89"/>
-      <c r="G89" t="s">
-        <v>62</v>
-      </c>
+      <c r="G89"/>
       <c r="H89"/>
       <c r="I89"/>
       <c r="J89"/>
       <c r="K89"/>
       <c r="L89"/>
-      <c r="M89"/>
+      <c r="M89" t="n">
+        <v>4</v>
+      </c>
       <c r="N89"/>
-      <c r="O89" t="n">
-        <v>4</v>
-      </c>
-      <c r="P89"/>
     </row>
     <row r="90">
-      <c r="A90"/>
+      <c r="A90" t="s">
+        <v>643</v>
+      </c>
       <c r="B90" t="s">
-        <v>619</v>
+        <v>644</v>
       </c>
       <c r="C90" t="s">
-        <v>649</v>
-      </c>
-      <c r="D90" t="s">
-        <v>650</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D90"/>
       <c r="E90" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F90"/>
-      <c r="G90" t="s">
-        <v>62</v>
-      </c>
+      <c r="G90"/>
       <c r="H90"/>
       <c r="I90"/>
-      <c r="J90"/>
+      <c r="J90" t="s">
+        <v>469</v>
+      </c>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>472</v>
-      </c>
-      <c r="M90"/>
-      <c r="N90" t="s">
-        <v>473</v>
-      </c>
-      <c r="O90" t="n">
-        <v>4</v>
-      </c>
-      <c r="P90"/>
+        <v>470</v>
+      </c>
+      <c r="M90" t="n">
+        <v>4</v>
+      </c>
+      <c r="N90"/>
     </row>
     <row r="91">
-      <c r="A91"/>
+      <c r="A91" t="s">
+        <v>645</v>
+      </c>
       <c r="B91" t="s">
-        <v>619</v>
+        <v>646</v>
       </c>
       <c r="C91" t="s">
-        <v>651</v>
-      </c>
-      <c r="D91" t="s">
-        <v>652</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D91"/>
       <c r="E91" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F91"/>
-      <c r="G91" t="s">
-        <v>62</v>
-      </c>
+      <c r="G91"/>
       <c r="H91"/>
       <c r="I91"/>
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91"/>
-      <c r="M91"/>
+      <c r="M91" t="n">
+        <v>4</v>
+      </c>
       <c r="N91"/>
-      <c r="O91" t="n">
-        <v>4</v>
-      </c>
-      <c r="P91"/>
     </row>
     <row r="92">
-      <c r="A92"/>
+      <c r="A92" t="s">
+        <v>647</v>
+      </c>
       <c r="B92" t="s">
-        <v>619</v>
+        <v>648</v>
       </c>
       <c r="C92" t="s">
-        <v>653</v>
-      </c>
-      <c r="D92" t="s">
-        <v>654</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D92"/>
       <c r="E92" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F92"/>
-      <c r="G92" t="s">
-        <v>62</v>
-      </c>
+      <c r="G92"/>
       <c r="H92"/>
       <c r="I92"/>
       <c r="J92"/>
       <c r="K92"/>
       <c r="L92"/>
-      <c r="M92"/>
+      <c r="M92" t="n">
+        <v>4</v>
+      </c>
       <c r="N92"/>
-      <c r="O92" t="n">
-        <v>4</v>
-      </c>
-      <c r="P92"/>
     </row>
     <row r="93">
-      <c r="A93"/>
+      <c r="A93" t="s">
+        <v>649</v>
+      </c>
       <c r="B93" t="s">
-        <v>619</v>
+        <v>650</v>
       </c>
       <c r="C93" t="s">
-        <v>655</v>
-      </c>
-      <c r="D93" t="s">
-        <v>656</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D93"/>
       <c r="E93" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F93"/>
-      <c r="G93" t="s">
-        <v>62</v>
-      </c>
+      <c r="G93"/>
       <c r="H93"/>
       <c r="I93"/>
-      <c r="J93"/>
+      <c r="J93" t="s">
+        <v>29</v>
+      </c>
       <c r="K93"/>
       <c r="L93" t="s">
-        <v>29</v>
-      </c>
-      <c r="M93"/>
-      <c r="N93" t="s">
-        <v>473</v>
-      </c>
-      <c r="O93" t="n">
-        <v>4</v>
-      </c>
-      <c r="P93"/>
+        <v>470</v>
+      </c>
+      <c r="M93" t="n">
+        <v>4</v>
+      </c>
+      <c r="N93"/>
     </row>
     <row r="94">
-      <c r="A94"/>
+      <c r="A94" t="s">
+        <v>651</v>
+      </c>
       <c r="B94" t="s">
-        <v>619</v>
+        <v>652</v>
       </c>
       <c r="C94" t="s">
-        <v>657</v>
-      </c>
-      <c r="D94" t="s">
-        <v>658</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D94"/>
       <c r="E94" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F94"/>
-      <c r="G94" t="s">
-        <v>62</v>
-      </c>
+      <c r="G94"/>
       <c r="H94"/>
       <c r="I94"/>
       <c r="J94"/>
       <c r="K94"/>
       <c r="L94"/>
-      <c r="M94"/>
+      <c r="M94" t="n">
+        <v>4</v>
+      </c>
       <c r="N94"/>
-      <c r="O94" t="n">
-        <v>4</v>
-      </c>
-      <c r="P94"/>
     </row>
     <row r="95">
-      <c r="A95"/>
+      <c r="A95" t="s">
+        <v>653</v>
+      </c>
       <c r="B95" t="s">
-        <v>619</v>
+        <v>654</v>
       </c>
       <c r="C95" t="s">
-        <v>659</v>
-      </c>
-      <c r="D95" t="s">
-        <v>660</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D95"/>
       <c r="E95" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F95"/>
-      <c r="G95" t="s">
-        <v>62</v>
-      </c>
+      <c r="G95"/>
       <c r="H95"/>
       <c r="I95"/>
       <c r="J95"/>
       <c r="K95"/>
       <c r="L95"/>
-      <c r="M95"/>
+      <c r="M95" t="n">
+        <v>4</v>
+      </c>
       <c r="N95"/>
-      <c r="O95" t="n">
-        <v>4</v>
-      </c>
-      <c r="P95"/>
     </row>
     <row r="96">
-      <c r="A96"/>
+      <c r="A96" t="s">
+        <v>655</v>
+      </c>
       <c r="B96" t="s">
-        <v>619</v>
+        <v>656</v>
       </c>
       <c r="C96" t="s">
-        <v>661</v>
-      </c>
-      <c r="D96" t="s">
-        <v>662</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D96"/>
       <c r="E96" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F96"/>
-      <c r="G96" t="s">
-        <v>62</v>
-      </c>
+      <c r="G96"/>
       <c r="H96"/>
       <c r="I96"/>
-      <c r="J96"/>
+      <c r="J96" t="s">
+        <v>29</v>
+      </c>
       <c r="K96"/>
       <c r="L96" t="s">
-        <v>29</v>
-      </c>
-      <c r="M96"/>
-      <c r="N96" t="s">
-        <v>473</v>
-      </c>
-      <c r="O96" t="n">
-        <v>4</v>
-      </c>
-      <c r="P96"/>
+        <v>470</v>
+      </c>
+      <c r="M96" t="n">
+        <v>4</v>
+      </c>
+      <c r="N96"/>
     </row>
     <row r="97">
-      <c r="A97"/>
+      <c r="A97" t="s">
+        <v>657</v>
+      </c>
       <c r="B97" t="s">
-        <v>619</v>
+        <v>658</v>
       </c>
       <c r="C97" t="s">
-        <v>663</v>
-      </c>
-      <c r="D97" t="s">
-        <v>664</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D97"/>
       <c r="E97" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F97"/>
-      <c r="G97" t="s">
-        <v>62</v>
-      </c>
+      <c r="G97"/>
       <c r="H97"/>
       <c r="I97"/>
       <c r="J97"/>
       <c r="K97"/>
       <c r="L97"/>
-      <c r="M97"/>
+      <c r="M97" t="n">
+        <v>4</v>
+      </c>
       <c r="N97"/>
-      <c r="O97" t="n">
-        <v>4</v>
-      </c>
-      <c r="P97"/>
     </row>
     <row r="98">
-      <c r="A98"/>
+      <c r="A98" t="s">
+        <v>659</v>
+      </c>
       <c r="B98" t="s">
-        <v>619</v>
+        <v>660</v>
       </c>
       <c r="C98" t="s">
-        <v>665</v>
-      </c>
-      <c r="D98" t="s">
-        <v>666</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D98"/>
       <c r="E98" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F98"/>
-      <c r="G98" t="s">
-        <v>62</v>
-      </c>
+      <c r="G98"/>
       <c r="H98"/>
       <c r="I98"/>
       <c r="J98"/>
       <c r="K98"/>
       <c r="L98"/>
-      <c r="M98"/>
+      <c r="M98" t="n">
+        <v>4</v>
+      </c>
       <c r="N98"/>
-      <c r="O98" t="n">
-        <v>4</v>
-      </c>
-      <c r="P98"/>
     </row>
     <row r="99">
-      <c r="A99"/>
+      <c r="A99" t="s">
+        <v>661</v>
+      </c>
       <c r="B99" t="s">
-        <v>619</v>
+        <v>662</v>
       </c>
       <c r="C99" t="s">
-        <v>667</v>
-      </c>
-      <c r="D99" t="s">
-        <v>668</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D99"/>
       <c r="E99" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F99"/>
-      <c r="G99" t="s">
-        <v>62</v>
-      </c>
+      <c r="G99"/>
       <c r="H99"/>
       <c r="I99"/>
-      <c r="J99"/>
+      <c r="J99" t="s">
+        <v>29</v>
+      </c>
       <c r="K99"/>
       <c r="L99" t="s">
-        <v>29</v>
-      </c>
-      <c r="M99"/>
-      <c r="N99" t="s">
-        <v>473</v>
-      </c>
-      <c r="O99" t="n">
-        <v>4</v>
-      </c>
-      <c r="P99"/>
+        <v>470</v>
+      </c>
+      <c r="M99" t="n">
+        <v>4</v>
+      </c>
+      <c r="N99"/>
     </row>
     <row r="100">
-      <c r="A100"/>
+      <c r="A100" t="s">
+        <v>663</v>
+      </c>
       <c r="B100" t="s">
-        <v>619</v>
+        <v>664</v>
       </c>
       <c r="C100" t="s">
-        <v>669</v>
-      </c>
-      <c r="D100" t="s">
-        <v>670</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D100"/>
       <c r="E100" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F100"/>
-      <c r="G100" t="s">
-        <v>62</v>
-      </c>
+      <c r="G100"/>
       <c r="H100"/>
       <c r="I100"/>
       <c r="J100"/>
       <c r="K100"/>
       <c r="L100"/>
-      <c r="M100"/>
+      <c r="M100" t="n">
+        <v>4</v>
+      </c>
       <c r="N100"/>
-      <c r="O100" t="n">
-        <v>4</v>
-      </c>
-      <c r="P100"/>
     </row>
     <row r="101">
-      <c r="A101"/>
+      <c r="A101" t="s">
+        <v>665</v>
+      </c>
       <c r="B101" t="s">
-        <v>619</v>
+        <v>666</v>
       </c>
       <c r="C101" t="s">
-        <v>671</v>
-      </c>
-      <c r="D101" t="s">
-        <v>672</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D101"/>
       <c r="E101" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F101"/>
-      <c r="G101" t="s">
-        <v>62</v>
-      </c>
+      <c r="G101"/>
       <c r="H101"/>
       <c r="I101"/>
       <c r="J101"/>
       <c r="K101"/>
       <c r="L101"/>
-      <c r="M101"/>
+      <c r="M101" t="n">
+        <v>4</v>
+      </c>
       <c r="N101"/>
-      <c r="O101" t="n">
-        <v>4</v>
-      </c>
-      <c r="P101"/>
     </row>
     <row r="102">
-      <c r="A102"/>
+      <c r="A102" t="s">
+        <v>667</v>
+      </c>
       <c r="B102" t="s">
-        <v>619</v>
+        <v>668</v>
       </c>
       <c r="C102" t="s">
-        <v>673</v>
-      </c>
-      <c r="D102" t="s">
-        <v>674</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D102"/>
       <c r="E102" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F102"/>
-      <c r="G102" t="s">
-        <v>62</v>
-      </c>
+      <c r="G102"/>
       <c r="H102"/>
       <c r="I102"/>
-      <c r="J102"/>
+      <c r="J102" t="s">
+        <v>29</v>
+      </c>
       <c r="K102"/>
       <c r="L102" t="s">
-        <v>29</v>
-      </c>
-      <c r="M102"/>
-      <c r="N102" t="s">
-        <v>473</v>
-      </c>
-      <c r="O102" t="n">
-        <v>4</v>
-      </c>
-      <c r="P102"/>
+        <v>470</v>
+      </c>
+      <c r="M102" t="n">
+        <v>4</v>
+      </c>
+      <c r="N102"/>
     </row>
     <row r="103">
-      <c r="A103"/>
+      <c r="A103" t="s">
+        <v>669</v>
+      </c>
       <c r="B103" t="s">
-        <v>619</v>
+        <v>670</v>
       </c>
       <c r="C103" t="s">
-        <v>675</v>
-      </c>
-      <c r="D103" t="s">
-        <v>676</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D103"/>
       <c r="E103" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F103"/>
-      <c r="G103" t="s">
-        <v>62</v>
-      </c>
+      <c r="G103"/>
       <c r="H103"/>
       <c r="I103"/>
       <c r="J103"/>
       <c r="K103"/>
       <c r="L103"/>
-      <c r="M103"/>
+      <c r="M103" t="n">
+        <v>4</v>
+      </c>
       <c r="N103"/>
-      <c r="O103" t="n">
-        <v>4</v>
-      </c>
-      <c r="P103"/>
     </row>
     <row r="104">
-      <c r="A104"/>
+      <c r="A104" t="s">
+        <v>671</v>
+      </c>
       <c r="B104" t="s">
-        <v>619</v>
+        <v>672</v>
       </c>
       <c r="C104" t="s">
-        <v>677</v>
-      </c>
-      <c r="D104" t="s">
-        <v>678</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D104"/>
       <c r="E104" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F104"/>
-      <c r="G104" t="s">
-        <v>62</v>
-      </c>
+      <c r="G104"/>
       <c r="H104"/>
       <c r="I104"/>
       <c r="J104"/>
       <c r="K104"/>
       <c r="L104"/>
-      <c r="M104"/>
+      <c r="M104" t="n">
+        <v>4</v>
+      </c>
       <c r="N104"/>
-      <c r="O104" t="n">
-        <v>4</v>
-      </c>
-      <c r="P104"/>
     </row>
     <row r="105">
-      <c r="A105"/>
+      <c r="A105" t="s">
+        <v>673</v>
+      </c>
       <c r="B105" t="s">
-        <v>619</v>
+        <v>674</v>
       </c>
       <c r="C105" t="s">
-        <v>679</v>
-      </c>
-      <c r="D105" t="s">
-        <v>680</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D105"/>
       <c r="E105" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F105"/>
-      <c r="G105" t="s">
-        <v>62</v>
-      </c>
+      <c r="G105"/>
       <c r="H105"/>
       <c r="I105"/>
-      <c r="J105"/>
+      <c r="J105" t="s">
+        <v>29</v>
+      </c>
       <c r="K105"/>
       <c r="L105" t="s">
-        <v>29</v>
-      </c>
-      <c r="M105"/>
-      <c r="N105" t="s">
-        <v>473</v>
-      </c>
-      <c r="O105" t="n">
-        <v>4</v>
-      </c>
-      <c r="P105"/>
+        <v>470</v>
+      </c>
+      <c r="M105" t="n">
+        <v>4</v>
+      </c>
+      <c r="N105"/>
     </row>
     <row r="106">
-      <c r="A106"/>
+      <c r="A106" t="s">
+        <v>675</v>
+      </c>
       <c r="B106" t="s">
-        <v>619</v>
+        <v>676</v>
       </c>
       <c r="C106" t="s">
-        <v>681</v>
-      </c>
-      <c r="D106" t="s">
-        <v>682</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D106"/>
       <c r="E106" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F106"/>
-      <c r="G106" t="s">
-        <v>62</v>
-      </c>
+      <c r="G106"/>
       <c r="H106"/>
       <c r="I106"/>
       <c r="J106"/>
       <c r="K106"/>
       <c r="L106"/>
-      <c r="M106"/>
+      <c r="M106" t="n">
+        <v>4</v>
+      </c>
       <c r="N106"/>
-      <c r="O106" t="n">
-        <v>4</v>
-      </c>
-      <c r="P106"/>
     </row>
     <row r="107">
-      <c r="A107"/>
+      <c r="A107" t="s">
+        <v>677</v>
+      </c>
       <c r="B107" t="s">
-        <v>619</v>
+        <v>678</v>
       </c>
       <c r="C107" t="s">
-        <v>683</v>
-      </c>
-      <c r="D107" t="s">
-        <v>684</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D107"/>
       <c r="E107" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F107"/>
-      <c r="G107" t="s">
-        <v>62</v>
-      </c>
+      <c r="G107"/>
       <c r="H107"/>
       <c r="I107"/>
       <c r="J107"/>
       <c r="K107"/>
       <c r="L107"/>
-      <c r="M107"/>
+      <c r="M107" t="n">
+        <v>4</v>
+      </c>
       <c r="N107"/>
-      <c r="O107" t="n">
-        <v>4</v>
-      </c>
-      <c r="P107"/>
     </row>
     <row r="108">
-      <c r="A108"/>
+      <c r="A108" t="s">
+        <v>679</v>
+      </c>
       <c r="B108" t="s">
-        <v>619</v>
-      </c>
-      <c r="C108" t="s">
-        <v>685</v>
-      </c>
-      <c r="D108" t="s">
-        <v>686</v>
-      </c>
-      <c r="E108"/>
+        <v>680</v>
+      </c>
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108" t="s">
+        <v>62</v>
+      </c>
       <c r="F108"/>
-      <c r="G108" t="s">
-        <v>62</v>
-      </c>
+      <c r="G108"/>
       <c r="H108"/>
       <c r="I108"/>
-      <c r="J108"/>
+      <c r="J108" t="s">
+        <v>29</v>
+      </c>
       <c r="K108"/>
       <c r="L108" t="s">
-        <v>29</v>
-      </c>
-      <c r="M108"/>
-      <c r="N108" t="s">
-        <v>473</v>
-      </c>
-      <c r="O108" t="n">
-        <v>4</v>
-      </c>
-      <c r="P108"/>
+        <v>470</v>
+      </c>
+      <c r="M108" t="n">
+        <v>4</v>
+      </c>
+      <c r="N108"/>
     </row>
     <row r="109">
-      <c r="A109"/>
+      <c r="A109" t="s">
+        <v>681</v>
+      </c>
       <c r="B109" t="s">
-        <v>619</v>
-      </c>
-      <c r="C109" t="s">
-        <v>687</v>
-      </c>
-      <c r="D109" t="s">
-        <v>688</v>
-      </c>
-      <c r="E109"/>
+        <v>682</v>
+      </c>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109" t="s">
+        <v>62</v>
+      </c>
       <c r="F109"/>
-      <c r="G109" t="s">
-        <v>62</v>
-      </c>
+      <c r="G109"/>
       <c r="H109"/>
       <c r="I109"/>
       <c r="J109"/>
       <c r="K109"/>
       <c r="L109"/>
-      <c r="M109"/>
+      <c r="M109" t="n">
+        <v>4</v>
+      </c>
       <c r="N109"/>
-      <c r="O109" t="n">
-        <v>4</v>
-      </c>
-      <c r="P109"/>
     </row>
     <row r="110">
-      <c r="A110"/>
+      <c r="A110" t="s">
+        <v>683</v>
+      </c>
       <c r="B110" t="s">
-        <v>619</v>
-      </c>
-      <c r="C110" t="s">
-        <v>689</v>
-      </c>
-      <c r="D110" t="s">
-        <v>690</v>
-      </c>
-      <c r="E110"/>
+        <v>684</v>
+      </c>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110" t="s">
+        <v>62</v>
+      </c>
       <c r="F110"/>
-      <c r="G110" t="s">
-        <v>62</v>
-      </c>
+      <c r="G110"/>
       <c r="H110"/>
       <c r="I110"/>
       <c r="J110"/>
       <c r="K110"/>
       <c r="L110"/>
-      <c r="M110"/>
+      <c r="M110" t="n">
+        <v>4</v>
+      </c>
       <c r="N110"/>
-      <c r="O110" t="n">
-        <v>4</v>
-      </c>
-      <c r="P110"/>
     </row>
     <row r="111">
-      <c r="A111"/>
+      <c r="A111" t="s">
+        <v>685</v>
+      </c>
       <c r="B111" t="s">
-        <v>619</v>
-      </c>
-      <c r="C111" t="s">
-        <v>691</v>
-      </c>
-      <c r="D111" t="s">
-        <v>692</v>
-      </c>
-      <c r="E111"/>
+        <v>686</v>
+      </c>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111" t="s">
+        <v>62</v>
+      </c>
       <c r="F111"/>
-      <c r="G111" t="s">
-        <v>62</v>
-      </c>
+      <c r="G111"/>
       <c r="H111"/>
       <c r="I111"/>
-      <c r="J111"/>
+      <c r="J111" t="s">
+        <v>29</v>
+      </c>
       <c r="K111"/>
       <c r="L111" t="s">
-        <v>29</v>
-      </c>
-      <c r="M111"/>
-      <c r="N111" t="s">
-        <v>473</v>
-      </c>
-      <c r="O111" t="n">
-        <v>4</v>
-      </c>
-      <c r="P111"/>
+        <v>470</v>
+      </c>
+      <c r="M111" t="n">
+        <v>4</v>
+      </c>
+      <c r="N111"/>
     </row>
     <row r="112">
-      <c r="A112"/>
+      <c r="A112" t="s">
+        <v>687</v>
+      </c>
       <c r="B112" t="s">
-        <v>619</v>
-      </c>
-      <c r="C112" t="s">
-        <v>693</v>
-      </c>
-      <c r="D112" t="s">
-        <v>694</v>
-      </c>
-      <c r="E112"/>
+        <v>688</v>
+      </c>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112" t="s">
+        <v>62</v>
+      </c>
       <c r="F112"/>
-      <c r="G112" t="s">
-        <v>62</v>
-      </c>
+      <c r="G112"/>
       <c r="H112"/>
       <c r="I112"/>
       <c r="J112"/>
       <c r="K112"/>
       <c r="L112"/>
-      <c r="M112"/>
+      <c r="M112" t="n">
+        <v>4</v>
+      </c>
       <c r="N112"/>
-      <c r="O112" t="n">
-        <v>4</v>
-      </c>
-      <c r="P112"/>
     </row>
     <row r="113">
-      <c r="A113"/>
+      <c r="A113" t="s">
+        <v>689</v>
+      </c>
       <c r="B113" t="s">
-        <v>619</v>
-      </c>
-      <c r="C113" t="s">
-        <v>695</v>
-      </c>
-      <c r="D113" t="s">
-        <v>696</v>
-      </c>
-      <c r="E113"/>
+        <v>690</v>
+      </c>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113" t="s">
+        <v>62</v>
+      </c>
       <c r="F113"/>
-      <c r="G113" t="s">
-        <v>62</v>
-      </c>
+      <c r="G113"/>
       <c r="H113"/>
       <c r="I113"/>
       <c r="J113"/>
       <c r="K113"/>
       <c r="L113"/>
-      <c r="M113"/>
+      <c r="M113" t="n">
+        <v>4</v>
+      </c>
       <c r="N113"/>
-      <c r="O113" t="n">
-        <v>4</v>
-      </c>
-      <c r="P113"/>
     </row>
     <row r="114">
-      <c r="A114"/>
+      <c r="A114" t="s">
+        <v>691</v>
+      </c>
       <c r="B114" t="s">
-        <v>619</v>
-      </c>
-      <c r="C114" t="s">
-        <v>697</v>
-      </c>
-      <c r="D114" t="s">
-        <v>698</v>
-      </c>
-      <c r="E114"/>
+        <v>692</v>
+      </c>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114" t="s">
+        <v>62</v>
+      </c>
       <c r="F114"/>
-      <c r="G114" t="s">
-        <v>62</v>
-      </c>
+      <c r="G114"/>
       <c r="H114"/>
       <c r="I114"/>
-      <c r="J114"/>
+      <c r="J114" t="s">
+        <v>29</v>
+      </c>
       <c r="K114"/>
       <c r="L114" t="s">
-        <v>29</v>
-      </c>
-      <c r="M114"/>
-      <c r="N114" t="s">
-        <v>473</v>
-      </c>
-      <c r="O114" t="n">
-        <v>4</v>
-      </c>
-      <c r="P114"/>
+        <v>470</v>
+      </c>
+      <c r="M114" t="n">
+        <v>4</v>
+      </c>
+      <c r="N114"/>
     </row>
     <row r="115">
-      <c r="A115"/>
+      <c r="A115" t="s">
+        <v>693</v>
+      </c>
       <c r="B115" t="s">
-        <v>619</v>
-      </c>
-      <c r="C115" t="s">
-        <v>699</v>
-      </c>
-      <c r="D115" t="s">
-        <v>700</v>
-      </c>
-      <c r="E115"/>
+        <v>694</v>
+      </c>
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115" t="s">
+        <v>62</v>
+      </c>
       <c r="F115"/>
-      <c r="G115" t="s">
-        <v>62</v>
-      </c>
+      <c r="G115"/>
       <c r="H115"/>
       <c r="I115"/>
       <c r="J115"/>
       <c r="K115"/>
       <c r="L115"/>
-      <c r="M115"/>
+      <c r="M115" t="n">
+        <v>4</v>
+      </c>
       <c r="N115"/>
-      <c r="O115" t="n">
-        <v>4</v>
-      </c>
-      <c r="P115"/>
     </row>
     <row r="116">
-      <c r="A116"/>
+      <c r="A116" t="s">
+        <v>695</v>
+      </c>
       <c r="B116" t="s">
-        <v>619</v>
-      </c>
-      <c r="C116" t="s">
-        <v>701</v>
-      </c>
-      <c r="D116" t="s">
-        <v>702</v>
-      </c>
-      <c r="E116"/>
+        <v>696</v>
+      </c>
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116" t="s">
+        <v>62</v>
+      </c>
       <c r="F116"/>
-      <c r="G116" t="s">
-        <v>62</v>
-      </c>
+      <c r="G116"/>
       <c r="H116"/>
       <c r="I116"/>
       <c r="J116"/>
       <c r="K116"/>
       <c r="L116"/>
-      <c r="M116"/>
+      <c r="M116" t="n">
+        <v>4</v>
+      </c>
       <c r="N116"/>
-      <c r="O116" t="n">
-        <v>4</v>
-      </c>
-      <c r="P116"/>
     </row>
     <row r="117">
-      <c r="A117"/>
+      <c r="A117" t="s">
+        <v>697</v>
+      </c>
       <c r="B117" t="s">
-        <v>619</v>
-      </c>
-      <c r="C117" t="s">
-        <v>703</v>
-      </c>
-      <c r="D117" t="s">
-        <v>704</v>
-      </c>
-      <c r="E117"/>
+        <v>698</v>
+      </c>
+      <c r="C117"/>
+      <c r="D117"/>
+      <c r="E117" t="s">
+        <v>62</v>
+      </c>
       <c r="F117"/>
-      <c r="G117" t="s">
-        <v>62</v>
-      </c>
+      <c r="G117"/>
       <c r="H117"/>
       <c r="I117"/>
-      <c r="J117"/>
+      <c r="J117" t="s">
+        <v>29</v>
+      </c>
       <c r="K117"/>
       <c r="L117" t="s">
-        <v>29</v>
-      </c>
-      <c r="M117"/>
-      <c r="N117" t="s">
-        <v>473</v>
-      </c>
-      <c r="O117" t="n">
-        <v>4</v>
-      </c>
-      <c r="P117"/>
+        <v>470</v>
+      </c>
+      <c r="M117" t="n">
+        <v>4</v>
+      </c>
+      <c r="N117"/>
     </row>
     <row r="118">
-      <c r="A118"/>
+      <c r="A118" t="s">
+        <v>699</v>
+      </c>
       <c r="B118" t="s">
-        <v>619</v>
-      </c>
-      <c r="C118" t="s">
-        <v>705</v>
-      </c>
-      <c r="D118" t="s">
-        <v>706</v>
-      </c>
-      <c r="E118"/>
+        <v>700</v>
+      </c>
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118" t="s">
+        <v>62</v>
+      </c>
       <c r="F118"/>
-      <c r="G118" t="s">
-        <v>62</v>
-      </c>
+      <c r="G118"/>
       <c r="H118"/>
       <c r="I118"/>
       <c r="J118"/>
       <c r="K118"/>
       <c r="L118"/>
-      <c r="M118"/>
+      <c r="M118" t="n">
+        <v>4</v>
+      </c>
       <c r="N118"/>
-      <c r="O118" t="n">
-        <v>4</v>
-      </c>
-      <c r="P118"/>
     </row>
     <row r="119">
-      <c r="A119"/>
+      <c r="A119" t="s">
+        <v>701</v>
+      </c>
       <c r="B119" t="s">
-        <v>619</v>
-      </c>
-      <c r="C119" t="s">
-        <v>707</v>
-      </c>
-      <c r="D119" t="s">
-        <v>708</v>
-      </c>
-      <c r="E119"/>
+        <v>702</v>
+      </c>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119" t="s">
+        <v>62</v>
+      </c>
       <c r="F119"/>
-      <c r="G119" t="s">
-        <v>62</v>
-      </c>
+      <c r="G119"/>
       <c r="H119"/>
       <c r="I119"/>
       <c r="J119"/>
       <c r="K119"/>
       <c r="L119"/>
-      <c r="M119"/>
+      <c r="M119" t="n">
+        <v>4</v>
+      </c>
       <c r="N119"/>
-      <c r="O119" t="n">
-        <v>4</v>
-      </c>
-      <c r="P119"/>
-    </row>
-    <row r="120">
-      <c r="A120"/>
-      <c r="B120" t="s">
-        <v>619</v>
-      </c>
-      <c r="C120"/>
-      <c r="D120"/>
-      <c r="E120"/>
-      <c r="F120"/>
-      <c r="G120"/>
-      <c r="H120"/>
-      <c r="I120"/>
-      <c r="J120"/>
-      <c r="K120"/>
-      <c r="L120"/>
-      <c r="M120"/>
-      <c r="N120"/>
-      <c r="O120"/>
-      <c r="P120"/>
-    </row>
-    <row r="121">
-      <c r="A121"/>
-      <c r="B121" t="s">
-        <v>619</v>
-      </c>
-      <c r="C121"/>
-      <c r="D121"/>
-      <c r="E121"/>
-      <c r="F121"/>
-      <c r="G121"/>
-      <c r="H121"/>
-      <c r="I121"/>
-      <c r="J121"/>
-      <c r="K121"/>
-      <c r="L121"/>
-      <c r="M121"/>
-      <c r="N121"/>
-      <c r="O121"/>
-      <c r="P121"/>
-    </row>
-    <row r="122">
-      <c r="A122"/>
-      <c r="B122" t="s">
-        <v>619</v>
-      </c>
-      <c r="C122"/>
-      <c r="D122"/>
-      <c r="E122"/>
-      <c r="F122"/>
-      <c r="G122"/>
-      <c r="H122"/>
-      <c r="I122"/>
-      <c r="J122"/>
-      <c r="K122"/>
-      <c r="L122"/>
-      <c r="M122"/>
-      <c r="N122"/>
-      <c r="O122"/>
-      <c r="P122"/>
-    </row>
-    <row r="123">
-      <c r="A123"/>
-      <c r="B123" t="s">
-        <v>619</v>
-      </c>
-      <c r="C123"/>
-      <c r="D123"/>
-      <c r="E123"/>
-      <c r="F123"/>
-      <c r="G123"/>
-      <c r="H123"/>
-      <c r="I123"/>
-      <c r="J123"/>
-      <c r="K123"/>
-      <c r="L123"/>
-      <c r="M123"/>
-      <c r="N123"/>
-      <c r="O123"/>
-      <c r="P123"/>
-    </row>
-    <row r="124">
-      <c r="A124"/>
-      <c r="B124" t="s">
-        <v>709</v>
-      </c>
-      <c r="C124"/>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
-      <c r="G124"/>
-      <c r="H124"/>
-      <c r="I124"/>
-      <c r="J124"/>
-      <c r="K124"/>
-      <c r="L124"/>
-      <c r="M124"/>
-      <c r="N124"/>
-      <c r="O124"/>
-      <c r="P124"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12784,14 +12035,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="n">
@@ -12810,17 +12061,17 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="B4" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="C4" t="s">
         <v>56</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
@@ -12829,7 +12080,7 @@
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -12838,10 +12089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="B5" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="C5" t="s">
         <v>56</v>
@@ -12857,7 +12108,7 @@
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -12866,10 +12117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="B6" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="C6" t="s">
         <v>56</v>
@@ -12885,7 +12136,7 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="M6" t="n">
         <v>4</v>
@@ -12894,17 +12145,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="B7" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="C7" t="s">
         <v>56</v>
       </c>
       <c r="D7"/>
       <c r="E7" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="F7"/>
       <c r="G7"/>
@@ -12913,7 +12164,7 @@
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="M7" t="n">
         <v>4</v>
@@ -12922,10 +12173,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="B8" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="C8" t="s">
         <v>56</v>
@@ -12941,7 +12192,7 @@
       <c r="J8"/>
       <c r="K8"/>
       <c r="L8" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="M8" t="n">
         <v>4</v>
@@ -12950,10 +12201,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="B9" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="C9" t="s">
         <v>56</v>
@@ -12969,7 +12220,7 @@
       <c r="J9"/>
       <c r="K9"/>
       <c r="L9" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="M9" t="n">
         <v>4</v>
@@ -12978,17 +12229,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="B10" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="C10" t="s">
         <v>56</v>
       </c>
       <c r="D10"/>
       <c r="E10" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="F10"/>
       <c r="G10"/>
@@ -12997,7 +12248,7 @@
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="M10" t="n">
         <v>5</v>
@@ -13006,10 +12257,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="B11" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="C11" t="s">
         <v>56</v>
@@ -13025,7 +12276,7 @@
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="M11" t="n">
         <v>5</v>
@@ -13034,10 +12285,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="B12" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="C12" t="s">
         <v>56</v>
@@ -13053,7 +12304,7 @@
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="M12" t="n">
         <v>4</v>
@@ -13062,17 +12313,17 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B13" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="C13" t="s">
         <v>56</v>
       </c>
       <c r="D13"/>
       <c r="E13" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="F13"/>
       <c r="G13"/>
@@ -13081,7 +12332,7 @@
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="M13" t="n">
         <v>4</v>
@@ -13090,10 +12341,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="B14" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="C14" t="s">
         <v>56</v>
@@ -13109,7 +12360,7 @@
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
@@ -13118,10 +12369,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="B15" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="C15" t="s">
         <v>56</v>
@@ -13137,7 +12388,7 @@
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="M15" t="n">
         <v>4</v>
@@ -13146,17 +12397,17 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="B16" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="C16" t="s">
         <v>56</v>
       </c>
       <c r="D16"/>
       <c r="E16" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="F16"/>
       <c r="G16"/>
@@ -13165,7 +12416,7 @@
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
@@ -13174,10 +12425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="B17" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="C17" t="s">
         <v>56</v>
@@ -13193,7 +12444,7 @@
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
@@ -13202,10 +12453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="B18" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="C18" t="s">
         <v>56</v>
@@ -13221,7 +12472,7 @@
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="M18" t="n">
         <v>4</v>
@@ -13230,17 +12481,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="B19" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="C19" t="s">
         <v>56</v>
       </c>
       <c r="D19"/>
       <c r="E19" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="F19"/>
       <c r="G19"/>
@@ -13249,7 +12500,7 @@
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="M19" t="n">
         <v>4</v>
@@ -13258,10 +12509,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="B20" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="C20" t="s">
         <v>56</v>
@@ -13277,7 +12528,7 @@
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="M20" t="n">
         <v>4</v>
@@ -13286,17 +12537,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="B21" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="C21" t="s">
         <v>56</v>
       </c>
       <c r="D21"/>
       <c r="E21" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F21"/>
       <c r="G21"/>
@@ -13305,7 +12556,7 @@
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="M21" t="n">
         <v>4</v>
@@ -13314,17 +12565,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="B22" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="C22" t="s">
         <v>56</v>
       </c>
       <c r="D22"/>
       <c r="E22" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="F22"/>
       <c r="G22"/>
@@ -13333,7 +12584,7 @@
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="M22" t="n">
         <v>5</v>
@@ -13342,17 +12593,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="B23" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="C23" t="s">
         <v>56</v>
       </c>
       <c r="D23"/>
       <c r="E23" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F23"/>
       <c r="G23"/>
@@ -13361,7 +12612,7 @@
       <c r="J23"/>
       <c r="K23"/>
       <c r="L23" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="M23" t="n">
         <v>5</v>
@@ -13370,17 +12621,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="B24" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="C24" t="s">
         <v>56</v>
       </c>
       <c r="D24"/>
       <c r="E24" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F24"/>
       <c r="G24"/>
@@ -13389,7 +12640,7 @@
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="M24" t="n">
         <v>4</v>
@@ -13398,17 +12649,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="B25" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="C25" t="s">
         <v>56</v>
       </c>
       <c r="D25"/>
       <c r="E25" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="F25"/>
       <c r="G25"/>
@@ -13417,7 +12668,7 @@
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="M25" t="n">
         <v>4</v>
@@ -13426,17 +12677,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="B26" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="C26" t="s">
         <v>56</v>
       </c>
       <c r="D26"/>
       <c r="E26" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="F26"/>
       <c r="G26"/>
@@ -13445,7 +12696,7 @@
       <c r="J26"/>
       <c r="K26"/>
       <c r="L26" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="M26" t="n">
         <v>4</v>
@@ -13473,123 +12724,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="B1" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="C1" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="B2" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="C2" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="B3" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="C3" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="B4" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="C4" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="B5" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="C5" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="B6" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="C6" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="B7" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="C7" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="B8" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="C8" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="B9" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="C9" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="B10" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="C10" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="B11" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="C11" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
     </row>
   </sheetData>
@@ -13613,13 +12864,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="B1" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="C1" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
     </row>
     <row r="2">
@@ -13657,7 +12908,7 @@
         <v>43923</v>
       </c>
       <c r="C5" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
     </row>
     <row r="6">
@@ -13668,7 +12919,7 @@
         <v>44302</v>
       </c>
       <c r="C6" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
     </row>
     <row r="7">
@@ -13679,7 +12930,7 @@
         <v>44320</v>
       </c>
       <c r="C7" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/10.5281_zenodo.19682162/cb_hbm4eu_alignedstudies_adults.xlsx
+++ b/downloads/10.5281_zenodo.19682162/cb_hbm4eu_alignedstudies_adults.xlsx
@@ -3040,22 +3040,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="61.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="92.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="6.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="208.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="70.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="250.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="250.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -3684,14 +3668,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="33.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="7.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="15.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="87.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -3764,22 +3740,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="73.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="250.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="58.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="121.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -4040,22 +4000,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="250.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="5.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="115.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="236.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="250.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -8664,22 +8608,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="92.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="7.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="5.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="192.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="250.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -11944,22 +11872,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="142.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="131.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="7.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="70.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="19.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="250.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -12716,11 +12628,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="47.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="122.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -12856,11 +12763,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="6.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="8.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="53.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
